--- a/output/spreadsheets/Kavanah-Rabbinic-Hebrew-Review.xlsx
+++ b/output/spreadsheets/Kavanah-Rabbinic-Hebrew-Review.xlsx
@@ -9,12 +9,12 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start Here" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prayer Review" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Service Collections" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Service Index" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Prayer Review'!$A$1:$I$562</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Prayer Review'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Service Collections'!$A$4:$F$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Service Index'!$A$4:$F$192</definedName>
   </definedNames>
   <calcPr calcId="124519" calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -149,7 +149,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -199,6 +199,12 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -610,7 +616,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="62" customHeight="1">
+    <row r="7" ht="74" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
           <t>Service Collections</t>
@@ -618,7 +624,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Shacharit, Mincha, and Maariv are listed separately because they are service collections, not single prayers, and no single Hebrew candidate is ready for approval. These require a section-level review; leaving their notes blank does not approve them.</t>
+          <t>Shacharit, Mincha, and Maariv each contain many individual prayers. Their current catalog entries are indexed in the “Service Index” tab and link back to the single review row where Hebrew and comments live. This index is useful for navigation; full-service completeness still needs a separate edition and sequence review.</t>
         </is>
       </c>
     </row>
@@ -33674,157 +33680,5903 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="00B68532"/>
+    <tabColor rgb="0034685C"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F192"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="52" customWidth="1" min="4" max="4"/>
-    <col width="72" customWidth="1" min="5" max="5"/>
-    <col width="46" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="33" customWidth="1" min="2" max="2"/>
+    <col width="58" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="66" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="38" customHeight="1">
       <c r="A1" s="15" t="inlineStr">
         <is>
-          <t>Section-level review required</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="48" customHeight="1">
+          <t>Shacharit, Mincha &amp; Maariv | Prayer Index</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="50" customHeight="1">
       <c r="A2" s="16" t="inlineStr">
         <is>
-          <t>These three catalog entries represent full services, not individual prayer texts. The project review inventory says each needs a section-level source plan. No Hebrew candidate is ready; therefore these cannot be approved by leaving comments blank.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
+          <t>These are individual catalog entries whose source location places them in one of these services. Use “Open review row” to jump to the existing row in Prayer Review; enter comments there so each prayer has only one review record. This index does not certify that a complete service sequence or edition is ready for approval.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Review status</t>
+          <t>Service</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Prayer</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Proposed tradition</t>
+          <t>Catalog ID</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>Hebrew text</t>
+          <t>Prayer Review row</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>Source / review note</t>
+          <t>Source section</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Rabbi comments</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="60" customHeight="1">
-      <c r="A5" s="17" t="inlineStr">
-        <is>
-          <t>Section review required</t>
-        </is>
-      </c>
-      <c r="B5" s="17" t="inlineStr">
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="25" customHeight="1">
+      <c r="A5" s="12" t="inlineStr">
         <is>
           <t>Shacharit</t>
         </is>
       </c>
-      <c r="C5" s="17" t="inlineStr">
-        <is>
-          <t>Ashkenaz</t>
-        </is>
-      </c>
-      <c r="D5" s="17" t="inlineStr">
-        <is>
-          <t>No Hebrew candidate is ready for approval.</t>
-        </is>
-      </c>
-      <c r="E5" s="17" t="inlineStr">
-        <is>
-          <t>Siddur Ashkenaz, Weekday Shacharit. Service collection, not a single prayer. Source snapshot not yet pinned; section-level source plan required.</t>
-        </is>
-      </c>
-      <c r="F5" s="17" t="inlineStr"/>
-    </row>
-    <row r="6" ht="60" customHeight="1">
-      <c r="A6" s="17" t="inlineStr">
-        <is>
-          <t>Section review required</t>
-        </is>
-      </c>
-      <c r="B6" s="17" t="inlineStr">
+      <c r="B5" s="12" t="inlineStr">
+        <is>
+          <t>Second Blessing before Shema</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-ashkenaz-shabbat-shacharit-blessings-of-the-shema-second-blessing-before-shema</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="n">
+        <v>321</v>
+      </c>
+      <c r="E5" s="12" t="inlineStr">
+        <is>
+          <t>Shabbat / Shacharit / Blessings of the Shema / Second Blessing before Shema</t>
+        </is>
+      </c>
+      <c r="F5" s="18" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="25" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>Shacharit</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>Prayer for Israeli Soldiers</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-ashkenaz-shabbat-shacharit-communal-prayers-prayer-for-israeli-soldiers</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="n">
+        <v>322</v>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>Shabbat / Shacharit / Communal Prayers / Prayer for Israeli Soldiers</t>
+        </is>
+      </c>
+      <c r="F6" s="19" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="25" customHeight="1">
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>Shacharit</t>
+        </is>
+      </c>
+      <c r="B7" s="12" t="inlineStr">
+        <is>
+          <t>Prayer for Those Being Held in Captivity</t>
+        </is>
+      </c>
+      <c r="C7" s="12" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-ashkenaz-shabbat-shacharit-communal-prayers-prayer-for-those-being-held-in-captivity</t>
+        </is>
+      </c>
+      <c r="D7" s="12" t="n">
+        <v>323</v>
+      </c>
+      <c r="E7" s="12" t="inlineStr">
+        <is>
+          <t>Shabbat / Shacharit / Communal Prayers / Prayer for Those Being Held in Captivity</t>
+        </is>
+      </c>
+      <c r="F7" s="18" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="25" customHeight="1">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>Shacharit</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>Yishtabach</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-ashkenaz-shabbat-shacharit-pesukei-dezimra-yishtabach</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="n">
+        <v>320</v>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>Shabbat / Shacharit / Pesukei Dezimra / Yishtabach</t>
+        </is>
+      </c>
+      <c r="F8" s="19" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="25" customHeight="1">
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>Shacharit</t>
+        </is>
+      </c>
+      <c r="B9" s="12" t="inlineStr">
+        <is>
+          <t>Against Enemies</t>
+        </is>
+      </c>
+      <c r="C9" s="12" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-ashkenaz-weekday-shacharit-amidah-against-enemies</t>
+        </is>
+      </c>
+      <c r="D9" s="12" t="n">
+        <v>200</v>
+      </c>
+      <c r="E9" s="12" t="inlineStr">
+        <is>
+          <t>Weekday / Shacharit / Amidah / Against Enemies</t>
+        </is>
+      </c>
+      <c r="F9" s="18" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="25" customHeight="1">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>Shacharit</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>Birkat Kohanim</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-ashkenaz-weekday-shacharit-amidah-birkat-kohanim</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="n">
+        <v>206</v>
+      </c>
+      <c r="E10" s="8" t="inlineStr">
+        <is>
+          <t>Weekday / Shacharit / Amidah / Birkat Kohanim</t>
+        </is>
+      </c>
+      <c r="F10" s="19" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="25" customHeight="1">
+      <c r="A11" s="12" t="inlineStr">
+        <is>
+          <t>Shacharit</t>
+        </is>
+      </c>
+      <c r="B11" s="12" t="inlineStr">
+        <is>
+          <t>Concluding Passage</t>
+        </is>
+      </c>
+      <c r="C11" s="12" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-ashkenaz-weekday-shacharit-amidah-concluding-passage</t>
+        </is>
+      </c>
+      <c r="D11" s="12" t="n">
+        <v>207</v>
+      </c>
+      <c r="E11" s="12" t="inlineStr">
+        <is>
+          <t>Weekday / Shacharit / Amidah / Concluding Passage</t>
+        </is>
+      </c>
+      <c r="F11" s="18" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="25" customHeight="1">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>Shacharit</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>Forgiveness</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-ashkenaz-weekday-shacharit-amidah-forgiveness</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="n">
+        <v>197</v>
+      </c>
+      <c r="E12" s="8" t="inlineStr">
+        <is>
+          <t>Weekday / Shacharit / Amidah / Forgiveness</t>
+        </is>
+      </c>
+      <c r="F12" s="19" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="25" customHeight="1">
+      <c r="A13" s="12" t="inlineStr">
+        <is>
+          <t>Shacharit</t>
+        </is>
+      </c>
+      <c r="B13" s="12" t="inlineStr">
+        <is>
+          <t>Gathering the Exiles</t>
+        </is>
+      </c>
+      <c r="C13" s="12" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-ashkenaz-weekday-shacharit-amidah-gathering-the-exiles</t>
+        </is>
+      </c>
+      <c r="D13" s="12" t="n">
+        <v>199</v>
+      </c>
+      <c r="E13" s="12" t="inlineStr">
+        <is>
+          <t>Weekday / Shacharit / Amidah / Gathering the Exiles</t>
+        </is>
+      </c>
+      <c r="F13" s="18" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="25" customHeight="1">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>Shacharit</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>Healing</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-ashkenaz-weekday-shacharit-amidah-healing</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="n">
+        <v>198</v>
+      </c>
+      <c r="E14" s="8" t="inlineStr">
+        <is>
+          <t>Weekday / Shacharit / Amidah / Healing</t>
+        </is>
+      </c>
+      <c r="F14" s="19" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="25" customHeight="1">
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>Shacharit</t>
+        </is>
+      </c>
+      <c r="B15" s="12" t="inlineStr">
+        <is>
+          <t>Kedushah</t>
+        </is>
+      </c>
+      <c r="C15" s="12" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-ashkenaz-weekday-shacharit-amidah-kedushah</t>
+        </is>
+      </c>
+      <c r="D15" s="12" t="n">
+        <v>194</v>
+      </c>
+      <c r="E15" s="12" t="inlineStr">
+        <is>
+          <t>Weekday / Shacharit / Amidah / Kedushah</t>
+        </is>
+      </c>
+      <c r="F15" s="18" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="25" customHeight="1">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>Shacharit</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>Kingdom of David</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-ashkenaz-weekday-shacharit-amidah-kingdom-of-david</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="n">
+        <v>203</v>
+      </c>
+      <c r="E16" s="8" t="inlineStr">
+        <is>
+          <t>Weekday / Shacharit / Amidah / Kingdom of David</t>
+        </is>
+      </c>
+      <c r="F16" s="19" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="25" customHeight="1">
+      <c r="A17" s="12" t="inlineStr">
+        <is>
+          <t>Shacharit</t>
+        </is>
+      </c>
+      <c r="B17" s="12" t="inlineStr">
+        <is>
+          <t>Knowledge</t>
+        </is>
+      </c>
+      <c r="C17" s="12" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-ashkenaz-weekday-shacharit-amidah-knowledge</t>
+        </is>
+      </c>
+      <c r="D17" s="12" t="n">
+        <v>195</v>
+      </c>
+      <c r="E17" s="12" t="inlineStr">
+        <is>
+          <t>Weekday / Shacharit / Amidah / Knowledge</t>
+        </is>
+      </c>
+      <c r="F17" s="18" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="25" customHeight="1">
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t>Shacharit</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>Rebuilding Jerusalem</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-ashkenaz-weekday-shacharit-amidah-rebuilding-jerusalem</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="n">
+        <v>202</v>
+      </c>
+      <c r="E18" s="8" t="inlineStr">
+        <is>
+          <t>Weekday / Shacharit / Amidah / Rebuilding Jerusalem</t>
+        </is>
+      </c>
+      <c r="F18" s="19" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="25" customHeight="1">
+      <c r="A19" s="12" t="inlineStr">
+        <is>
+          <t>Shacharit</t>
+        </is>
+      </c>
+      <c r="B19" s="12" t="inlineStr">
+        <is>
+          <t>Repentance</t>
+        </is>
+      </c>
+      <c r="C19" s="12" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-ashkenaz-weekday-shacharit-amidah-repentance</t>
+        </is>
+      </c>
+      <c r="D19" s="12" t="n">
+        <v>196</v>
+      </c>
+      <c r="E19" s="12" t="inlineStr">
+        <is>
+          <t>Weekday / Shacharit / Amidah / Repentance</t>
+        </is>
+      </c>
+      <c r="F19" s="18" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="25" customHeight="1">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>Shacharit</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>Response to Prayer</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-ashkenaz-weekday-shacharit-amidah-response-to-prayer</t>
+        </is>
+      </c>
+      <c r="D20" s="8" t="n">
+        <v>204</v>
+      </c>
+      <c r="E20" s="8" t="inlineStr">
+        <is>
+          <t>Weekday / Shacharit / Amidah / Response to Prayer</t>
+        </is>
+      </c>
+      <c r="F20" s="19" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="25" customHeight="1">
+      <c r="A21" s="12" t="inlineStr">
+        <is>
+          <t>Shacharit</t>
+        </is>
+      </c>
+      <c r="B21" s="12" t="inlineStr">
+        <is>
+          <t>Temple Service</t>
+        </is>
+      </c>
+      <c r="C21" s="12" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-ashkenaz-weekday-shacharit-amidah-temple-service</t>
+        </is>
+      </c>
+      <c r="D21" s="12" t="n">
+        <v>205</v>
+      </c>
+      <c r="E21" s="12" t="inlineStr">
+        <is>
+          <t>Weekday / Shacharit / Amidah / Temple Service</t>
+        </is>
+      </c>
+      <c r="F21" s="18" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="25" customHeight="1">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>Shacharit</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>The Righteous</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-ashkenaz-weekday-shacharit-amidah-the-righteous</t>
+        </is>
+      </c>
+      <c r="D22" s="8" t="n">
+        <v>201</v>
+      </c>
+      <c r="E22" s="8" t="inlineStr">
+        <is>
+          <t>Weekday / Shacharit / Amidah / The Righteous</t>
+        </is>
+      </c>
+      <c r="F22" s="19" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="25" customHeight="1">
+      <c r="A23" s="12" t="inlineStr">
+        <is>
+          <t>Shacharit</t>
+        </is>
+      </c>
+      <c r="B23" s="12" t="inlineStr">
+        <is>
+          <t>Barchu</t>
+        </is>
+      </c>
+      <c r="C23" s="12" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-ashkenaz-weekday-shacharit-blessings-of-the-shema-barchu</t>
+        </is>
+      </c>
+      <c r="D23" s="12" t="n">
+        <v>190</v>
+      </c>
+      <c r="E23" s="12" t="inlineStr">
+        <is>
+          <t>Weekday / Shacharit / Blessings of the Shema / Barchu</t>
+        </is>
+      </c>
+      <c r="F23" s="18" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="25" customHeight="1">
+      <c r="A24" s="8" t="inlineStr">
+        <is>
+          <t>Shacharit</t>
+        </is>
+      </c>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>Blessing after Shema</t>
+        </is>
+      </c>
+      <c r="C24" s="8" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-ashkenaz-weekday-shacharit-blessings-of-the-shema-blessing-after-shema</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="n">
+        <v>193</v>
+      </c>
+      <c r="E24" s="8" t="inlineStr">
+        <is>
+          <t>Weekday / Shacharit / Blessings of the Shema / Blessing after Shema</t>
+        </is>
+      </c>
+      <c r="F24" s="19" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="25" customHeight="1">
+      <c r="A25" s="12" t="inlineStr">
+        <is>
+          <t>Shacharit</t>
+        </is>
+      </c>
+      <c r="B25" s="12" t="inlineStr">
+        <is>
+          <t>First Blessing before Shema</t>
+        </is>
+      </c>
+      <c r="C25" s="12" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-ashkenaz-weekday-shacharit-blessings-of-the-shema-first-blessing-before-shema</t>
+        </is>
+      </c>
+      <c r="D25" s="12" t="n">
+        <v>191</v>
+      </c>
+      <c r="E25" s="12" t="inlineStr">
+        <is>
+          <t>Weekday / Shacharit / Blessings of the Shema / First Blessing before Shema</t>
+        </is>
+      </c>
+      <c r="F25" s="18" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="25" customHeight="1">
+      <c r="A26" s="8" t="inlineStr">
+        <is>
+          <t>Shacharit</t>
+        </is>
+      </c>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>Second Blessing before Shema</t>
+        </is>
+      </c>
+      <c r="C26" s="8" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-ashkenaz-weekday-shacharit-blessings-of-the-shema-second-blessing-before-shema</t>
+        </is>
+      </c>
+      <c r="D26" s="8" t="n">
+        <v>192</v>
+      </c>
+      <c r="E26" s="8" t="inlineStr">
+        <is>
+          <t>Weekday / Shacharit / Blessings of the Shema / Second Blessing before Shema</t>
+        </is>
+      </c>
+      <c r="F26" s="19" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="25" customHeight="1">
+      <c r="A27" s="12" t="inlineStr">
+        <is>
+          <t>Shacharit</t>
+        </is>
+      </c>
+      <c r="B27" s="12" t="inlineStr">
+        <is>
+          <t>Shema</t>
+        </is>
+      </c>
+      <c r="C27" s="12" t="inlineStr">
+        <is>
+          <t>shema</t>
+        </is>
+      </c>
+      <c r="D27" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="E27" s="12" t="inlineStr">
+        <is>
+          <t>Weekday / Shacharit / Blessings of the Shema / Shema</t>
+        </is>
+      </c>
+      <c r="F27" s="18" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="25" customHeight="1">
+      <c r="A28" s="8" t="inlineStr">
+        <is>
+          <t>Shacharit</t>
+        </is>
+      </c>
+      <c r="B28" s="8" t="inlineStr">
+        <is>
+          <t>Alenu</t>
+        </is>
+      </c>
+      <c r="C28" s="8" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-ashkenaz-weekday-shacharit-concluding-prayers-alenu</t>
+        </is>
+      </c>
+      <c r="D28" s="8" t="n">
+        <v>229</v>
+      </c>
+      <c r="E28" s="8" t="inlineStr">
+        <is>
+          <t>Weekday / Shacharit / Concluding Prayers / Alenu</t>
+        </is>
+      </c>
+      <c r="F28" s="19" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="25" customHeight="1">
+      <c r="A29" s="12" t="inlineStr">
+        <is>
+          <t>Shacharit</t>
+        </is>
+      </c>
+      <c r="B29" s="12" t="inlineStr">
+        <is>
+          <t>Ashrei</t>
+        </is>
+      </c>
+      <c r="C29" s="12" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-ashkenaz-weekday-shacharit-concluding-prayers-ashrei</t>
+        </is>
+      </c>
+      <c r="D29" s="12" t="n">
+        <v>225</v>
+      </c>
+      <c r="E29" s="12" t="inlineStr">
+        <is>
+          <t>Weekday / Shacharit / Concluding Prayers / Ashrei</t>
+        </is>
+      </c>
+      <c r="F29" s="18" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="25" customHeight="1">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>Shacharit</t>
+        </is>
+      </c>
+      <c r="B30" s="8" t="inlineStr">
+        <is>
+          <t>Barchi Nafshi</t>
+        </is>
+      </c>
+      <c r="C30" s="8" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-ashkenaz-weekday-shacharit-concluding-prayers-barchi-nafshi</t>
+        </is>
+      </c>
+      <c r="D30" s="8" t="n">
+        <v>232</v>
+      </c>
+      <c r="E30" s="8" t="inlineStr">
+        <is>
+          <t>Weekday / Shacharit / Concluding Prayers / Barchi Nafshi</t>
+        </is>
+      </c>
+      <c r="F30" s="19" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="25" customHeight="1">
+      <c r="A31" s="12" t="inlineStr">
+        <is>
+          <t>Shacharit</t>
+        </is>
+      </c>
+      <c r="B31" s="12" t="inlineStr">
+        <is>
+          <t>Kaddish Shalem</t>
+        </is>
+      </c>
+      <c r="C31" s="12" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-ashkenaz-weekday-shacharit-concluding-prayers-kaddish-shalem</t>
+        </is>
+      </c>
+      <c r="D31" s="12" t="n">
+        <v>228</v>
+      </c>
+      <c r="E31" s="12" t="inlineStr">
+        <is>
+          <t>Weekday / Shacharit / Concluding Prayers / Kaddish Shalem</t>
+        </is>
+      </c>
+      <c r="F31" s="18" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="25" customHeight="1">
+      <c r="A32" s="8" t="inlineStr">
+        <is>
+          <t>Shacharit</t>
+        </is>
+      </c>
+      <c r="B32" s="8" t="inlineStr">
+        <is>
+          <t>Barchu</t>
+        </is>
+      </c>
+      <c r="C32" s="8" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-ashkenaz-weekday-shacharit-concluding-prayers-korbanot-israel-barchu</t>
+        </is>
+      </c>
+      <c r="D32" s="8" t="n">
+        <v>236</v>
+      </c>
+      <c r="E32" s="8" t="inlineStr">
+        <is>
+          <t>Weekday / Shacharit / Concluding Prayers / Korbanot (Israel) / Barchu</t>
+        </is>
+      </c>
+      <c r="F32" s="19" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="25" customHeight="1">
+      <c r="A33" s="12" t="inlineStr">
+        <is>
+          <t>Shacharit</t>
+        </is>
+      </c>
+      <c r="B33" s="12" t="inlineStr">
+        <is>
+          <t>Mourner's Kaddish</t>
+        </is>
+      </c>
+      <c r="C33" s="12" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-ashkenaz-weekday-shacharit-concluding-prayers-korbanot-israel-mourner-s-kaddish</t>
+        </is>
+      </c>
+      <c r="D33" s="12" t="n">
+        <v>235</v>
+      </c>
+      <c r="E33" s="12" t="inlineStr">
+        <is>
+          <t>Weekday / Shacharit / Concluding Prayers / Korbanot (Israel) / Mourner's Kaddish</t>
+        </is>
+      </c>
+      <c r="F33" s="18" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="25" customHeight="1">
+      <c r="A34" s="8" t="inlineStr">
+        <is>
+          <t>Shacharit</t>
+        </is>
+      </c>
+      <c r="B34" s="8" t="inlineStr">
+        <is>
+          <t>Pitum HaKetoret</t>
+        </is>
+      </c>
+      <c r="C34" s="8" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-ashkenaz-weekday-shacharit-concluding-prayers-korbanot-israel-pitum-haketoret</t>
+        </is>
+      </c>
+      <c r="D34" s="8" t="n">
+        <v>234</v>
+      </c>
+      <c r="E34" s="8" t="inlineStr">
+        <is>
+          <t>Weekday / Shacharit / Concluding Prayers / Korbanot (Israel) / Pitum HaKetoret</t>
+        </is>
+      </c>
+      <c r="F34" s="19" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="25" customHeight="1">
+      <c r="A35" s="12" t="inlineStr">
+        <is>
+          <t>Shacharit</t>
+        </is>
+      </c>
+      <c r="B35" s="12" t="inlineStr">
+        <is>
+          <t>Lamenatze'ach</t>
+        </is>
+      </c>
+      <c r="C35" s="12" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-ashkenaz-weekday-shacharit-concluding-prayers-lamenatze-ach</t>
+        </is>
+      </c>
+      <c r="D35" s="12" t="n">
+        <v>226</v>
+      </c>
+      <c r="E35" s="12" t="inlineStr">
+        <is>
+          <t>Weekday / Shacharit / Concluding Prayers / Lamenatze'ach</t>
+        </is>
+      </c>
+      <c r="F35" s="18" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="25" customHeight="1">
+      <c r="A36" s="8" t="inlineStr">
+        <is>
+          <t>Shacharit</t>
+        </is>
+      </c>
+      <c r="B36" s="8" t="inlineStr">
+        <is>
+          <t>LeDavid</t>
+        </is>
+      </c>
+      <c r="C36" s="8" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-ashkenaz-weekday-shacharit-concluding-prayers-ledavid</t>
+        </is>
+      </c>
+      <c r="D36" s="8" t="n">
+        <v>233</v>
+      </c>
+      <c r="E36" s="8" t="inlineStr">
+        <is>
+          <t>Weekday / Shacharit / Concluding Prayers / LeDavid</t>
+        </is>
+      </c>
+      <c r="F36" s="19" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="25" customHeight="1">
+      <c r="A37" s="12" t="inlineStr">
+        <is>
+          <t>Shacharit</t>
+        </is>
+      </c>
+      <c r="B37" s="12" t="inlineStr">
+        <is>
+          <t>Mourner's Kaddish</t>
+        </is>
+      </c>
+      <c r="C37" s="12" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-ashkenaz-weekday-shacharit-concluding-prayers-mourner-s-kaddish</t>
+        </is>
+      </c>
+      <c r="D37" s="12" t="n">
+        <v>230</v>
+      </c>
+      <c r="E37" s="12" t="inlineStr">
+        <is>
+          <t>Weekday / Shacharit / Concluding Prayers / Mourner's Kaddish</t>
+        </is>
+      </c>
+      <c r="F37" s="18" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="25" customHeight="1">
+      <c r="A38" s="8" t="inlineStr">
+        <is>
+          <t>Shacharit</t>
+        </is>
+      </c>
+      <c r="B38" s="8" t="inlineStr">
+        <is>
+          <t>Song of the Day</t>
+        </is>
+      </c>
+      <c r="C38" s="8" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-ashkenaz-weekday-shacharit-concluding-prayers-song-of-the-day</t>
+        </is>
+      </c>
+      <c r="D38" s="8" t="n">
+        <v>231</v>
+      </c>
+      <c r="E38" s="8" t="inlineStr">
+        <is>
+          <t>Weekday / Shacharit / Concluding Prayers / Song of the Day</t>
+        </is>
+      </c>
+      <c r="F38" s="19" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="25" customHeight="1">
+      <c r="A39" s="12" t="inlineStr">
+        <is>
+          <t>Shacharit</t>
+        </is>
+      </c>
+      <c r="B39" s="12" t="inlineStr">
+        <is>
+          <t>Uva Letzion</t>
+        </is>
+      </c>
+      <c r="C39" s="12" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-ashkenaz-weekday-shacharit-concluding-prayers-uva-letzion</t>
+        </is>
+      </c>
+      <c r="D39" s="12" t="n">
+        <v>227</v>
+      </c>
+      <c r="E39" s="12" t="inlineStr">
+        <is>
+          <t>Weekday / Shacharit / Concluding Prayers / Uva Letzion</t>
+        </is>
+      </c>
+      <c r="F39" s="18" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="25" customHeight="1">
+      <c r="A40" s="8" t="inlineStr">
+        <is>
+          <t>Shacharit</t>
+        </is>
+      </c>
+      <c r="B40" s="8" t="inlineStr">
+        <is>
+          <t>Ashrei</t>
+        </is>
+      </c>
+      <c r="C40" s="8" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-ashkenaz-weekday-shacharit-pesukei-dezimra-ashrei</t>
+        </is>
+      </c>
+      <c r="D40" s="8" t="n">
+        <v>177</v>
+      </c>
+      <c r="E40" s="8" t="inlineStr">
+        <is>
+          <t>Weekday / Shacharit / Pesukei Dezimra / Ashrei</t>
+        </is>
+      </c>
+      <c r="F40" s="19" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="25" customHeight="1">
+      <c r="A41" s="12" t="inlineStr">
+        <is>
+          <t>Shacharit</t>
+        </is>
+      </c>
+      <c r="B41" s="12" t="inlineStr">
+        <is>
+          <t>Ata Hu</t>
+        </is>
+      </c>
+      <c r="C41" s="12" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-ashkenaz-weekday-shacharit-pesukei-dezimra-ata-hu</t>
+        </is>
+      </c>
+      <c r="D41" s="12" t="n">
+        <v>185</v>
+      </c>
+      <c r="E41" s="12" t="inlineStr">
+        <is>
+          <t>Weekday / Shacharit / Pesukei Dezimra / Ata Hu</t>
+        </is>
+      </c>
+      <c r="F41" s="18" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="25" customHeight="1">
+      <c r="A42" s="8" t="inlineStr">
+        <is>
+          <t>Shacharit</t>
+        </is>
+      </c>
+      <c r="B42" s="8" t="inlineStr">
+        <is>
+          <t>Az Yashir</t>
+        </is>
+      </c>
+      <c r="C42" s="8" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-ashkenaz-weekday-shacharit-pesukei-dezimra-az-yashir</t>
+        </is>
+      </c>
+      <c r="D42" s="8" t="n">
+        <v>186</v>
+      </c>
+      <c r="E42" s="8" t="inlineStr">
+        <is>
+          <t>Weekday / Shacharit / Pesukei Dezimra / Az Yashir</t>
+        </is>
+      </c>
+      <c r="F42" s="19" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="25" customHeight="1">
+      <c r="A43" s="12" t="inlineStr">
+        <is>
+          <t>Shacharit</t>
+        </is>
+      </c>
+      <c r="B43" s="12" t="inlineStr">
+        <is>
+          <t>Barukh She'amar</t>
+        </is>
+      </c>
+      <c r="C43" s="12" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-ashkenaz-weekday-shacharit-pesukei-dezimra-barukh-she-amar</t>
+        </is>
+      </c>
+      <c r="D43" s="12" t="n">
+        <v>173</v>
+      </c>
+      <c r="E43" s="12" t="inlineStr">
+        <is>
+          <t>Weekday / Shacharit / Pesukei Dezimra / Barukh She'amar</t>
+        </is>
+      </c>
+      <c r="F43" s="18" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="25" customHeight="1">
+      <c r="A44" s="8" t="inlineStr">
+        <is>
+          <t>Shacharit</t>
+        </is>
+      </c>
+      <c r="B44" s="8" t="inlineStr">
+        <is>
+          <t>Closing Verses</t>
+        </is>
+      </c>
+      <c r="C44" s="8" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-ashkenaz-weekday-shacharit-pesukei-dezimra-closing-verses</t>
+        </is>
+      </c>
+      <c r="D44" s="8" t="n">
+        <v>183</v>
+      </c>
+      <c r="E44" s="8" t="inlineStr">
+        <is>
+          <t>Weekday / Shacharit / Pesukei Dezimra / Closing Verses</t>
+        </is>
+      </c>
+      <c r="F44" s="19" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="25" customHeight="1">
+      <c r="A45" s="12" t="inlineStr">
+        <is>
+          <t>Shacharit</t>
+        </is>
+      </c>
+      <c r="B45" s="12" t="inlineStr">
+        <is>
+          <t>Half Kaddish</t>
+        </is>
+      </c>
+      <c r="C45" s="12" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-ashkenaz-weekday-shacharit-pesukei-dezimra-half-kaddish</t>
+        </is>
+      </c>
+      <c r="D45" s="12" t="n">
+        <v>189</v>
+      </c>
+      <c r="E45" s="12" t="inlineStr">
+        <is>
+          <t>Weekday / Shacharit / Pesukei Dezimra / Half Kaddish</t>
+        </is>
+      </c>
+      <c r="F45" s="18" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="25" customHeight="1">
+      <c r="A46" s="8" t="inlineStr">
+        <is>
+          <t>Shacharit</t>
+        </is>
+      </c>
+      <c r="B46" s="8" t="inlineStr">
+        <is>
+          <t>Hodu</t>
+        </is>
+      </c>
+      <c r="C46" s="8" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-ashkenaz-weekday-shacharit-pesukei-dezimra-hodu</t>
+        </is>
+      </c>
+      <c r="D46" s="8" t="n">
+        <v>174</v>
+      </c>
+      <c r="E46" s="8" t="inlineStr">
+        <is>
+          <t>Weekday / Shacharit / Pesukei Dezimra / Hodu</t>
+        </is>
+      </c>
+      <c r="F46" s="19" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="25" customHeight="1">
+      <c r="A47" s="12" t="inlineStr">
+        <is>
+          <t>Shacharit</t>
+        </is>
+      </c>
+      <c r="B47" s="12" t="inlineStr">
+        <is>
+          <t>Introductory Psalm</t>
+        </is>
+      </c>
+      <c r="C47" s="12" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-ashkenaz-weekday-shacharit-pesukei-dezimra-introductory-psalm</t>
+        </is>
+      </c>
+      <c r="D47" s="12" t="n">
+        <v>171</v>
+      </c>
+      <c r="E47" s="12" t="inlineStr">
+        <is>
+          <t>Weekday / Shacharit / Pesukei Dezimra / Introductory Psalm</t>
+        </is>
+      </c>
+      <c r="F47" s="18" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="25" customHeight="1">
+      <c r="A48" s="8" t="inlineStr">
+        <is>
+          <t>Shacharit</t>
+        </is>
+      </c>
+      <c r="B48" s="8" t="inlineStr">
+        <is>
+          <t>Mizmor Letoda</t>
+        </is>
+      </c>
+      <c r="C48" s="8" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-ashkenaz-weekday-shacharit-pesukei-dezimra-mizmor-letoda</t>
+        </is>
+      </c>
+      <c r="D48" s="8" t="n">
+        <v>175</v>
+      </c>
+      <c r="E48" s="8" t="inlineStr">
+        <is>
+          <t>Weekday / Shacharit / Pesukei Dezimra / Mizmor Letoda</t>
+        </is>
+      </c>
+      <c r="F48" s="19" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="25" customHeight="1">
+      <c r="A49" s="12" t="inlineStr">
+        <is>
+          <t>Shacharit</t>
+        </is>
+      </c>
+      <c r="B49" s="12" t="inlineStr">
+        <is>
+          <t>Mourner's Kaddish</t>
+        </is>
+      </c>
+      <c r="C49" s="12" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-ashkenaz-weekday-shacharit-pesukei-dezimra-mourner-s-kaddish</t>
+        </is>
+      </c>
+      <c r="D49" s="12" t="n">
+        <v>172</v>
+      </c>
+      <c r="E49" s="12" t="inlineStr">
+        <is>
+          <t>Weekday / Shacharit / Pesukei Dezimra / Mourner's Kaddish</t>
+        </is>
+      </c>
+      <c r="F49" s="18" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="25" customHeight="1">
+      <c r="A50" s="8" t="inlineStr">
+        <is>
+          <t>Shacharit</t>
+        </is>
+      </c>
+      <c r="B50" s="8" t="inlineStr">
+        <is>
+          <t>Psalm 130</t>
+        </is>
+      </c>
+      <c r="C50" s="8" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-ashkenaz-weekday-shacharit-pesukei-dezimra-psalm-130</t>
+        </is>
+      </c>
+      <c r="D50" s="8" t="n">
+        <v>188</v>
+      </c>
+      <c r="E50" s="8" t="inlineStr">
+        <is>
+          <t>Weekday / Shacharit / Pesukei Dezimra / Psalm 130</t>
+        </is>
+      </c>
+      <c r="F50" s="19" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="25" customHeight="1">
+      <c r="A51" s="12" t="inlineStr">
+        <is>
+          <t>Shacharit</t>
+        </is>
+      </c>
+      <c r="B51" s="12" t="inlineStr">
+        <is>
+          <t>Psalm 146</t>
+        </is>
+      </c>
+      <c r="C51" s="12" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-ashkenaz-weekday-shacharit-pesukei-dezimra-psalm-146</t>
+        </is>
+      </c>
+      <c r="D51" s="12" t="n">
+        <v>178</v>
+      </c>
+      <c r="E51" s="12" t="inlineStr">
+        <is>
+          <t>Weekday / Shacharit / Pesukei Dezimra / Psalm 146</t>
+        </is>
+      </c>
+      <c r="F51" s="18" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="25" customHeight="1">
+      <c r="A52" s="8" t="inlineStr">
+        <is>
+          <t>Shacharit</t>
+        </is>
+      </c>
+      <c r="B52" s="8" t="inlineStr">
+        <is>
+          <t>Psalm 147</t>
+        </is>
+      </c>
+      <c r="C52" s="8" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-ashkenaz-weekday-shacharit-pesukei-dezimra-psalm-147</t>
+        </is>
+      </c>
+      <c r="D52" s="8" t="n">
+        <v>179</v>
+      </c>
+      <c r="E52" s="8" t="inlineStr">
+        <is>
+          <t>Weekday / Shacharit / Pesukei Dezimra / Psalm 147</t>
+        </is>
+      </c>
+      <c r="F52" s="19" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="25" customHeight="1">
+      <c r="A53" s="12" t="inlineStr">
+        <is>
+          <t>Shacharit</t>
+        </is>
+      </c>
+      <c r="B53" s="12" t="inlineStr">
+        <is>
+          <t>Psalm 148</t>
+        </is>
+      </c>
+      <c r="C53" s="12" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-ashkenaz-weekday-shacharit-pesukei-dezimra-psalm-148</t>
+        </is>
+      </c>
+      <c r="D53" s="12" t="n">
+        <v>180</v>
+      </c>
+      <c r="E53" s="12" t="inlineStr">
+        <is>
+          <t>Weekday / Shacharit / Pesukei Dezimra / Psalm 148</t>
+        </is>
+      </c>
+      <c r="F53" s="18" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="25" customHeight="1">
+      <c r="A54" s="8" t="inlineStr">
+        <is>
+          <t>Shacharit</t>
+        </is>
+      </c>
+      <c r="B54" s="8" t="inlineStr">
+        <is>
+          <t>Psalm 149</t>
+        </is>
+      </c>
+      <c r="C54" s="8" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-ashkenaz-weekday-shacharit-pesukei-dezimra-psalm-149</t>
+        </is>
+      </c>
+      <c r="D54" s="8" t="n">
+        <v>181</v>
+      </c>
+      <c r="E54" s="8" t="inlineStr">
+        <is>
+          <t>Weekday / Shacharit / Pesukei Dezimra / Psalm 149</t>
+        </is>
+      </c>
+      <c r="F54" s="19" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="25" customHeight="1">
+      <c r="A55" s="12" t="inlineStr">
+        <is>
+          <t>Shacharit</t>
+        </is>
+      </c>
+      <c r="B55" s="12" t="inlineStr">
+        <is>
+          <t>Psalm 150</t>
+        </is>
+      </c>
+      <c r="C55" s="12" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-ashkenaz-weekday-shacharit-pesukei-dezimra-psalm-150</t>
+        </is>
+      </c>
+      <c r="D55" s="12" t="n">
+        <v>182</v>
+      </c>
+      <c r="E55" s="12" t="inlineStr">
+        <is>
+          <t>Weekday / Shacharit / Pesukei Dezimra / Psalm 150</t>
+        </is>
+      </c>
+      <c r="F55" s="18" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="25" customHeight="1">
+      <c r="A56" s="8" t="inlineStr">
+        <is>
+          <t>Shacharit</t>
+        </is>
+      </c>
+      <c r="B56" s="8" t="inlineStr">
+        <is>
+          <t>Vayevarech David</t>
+        </is>
+      </c>
+      <c r="C56" s="8" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-ashkenaz-weekday-shacharit-pesukei-dezimra-vayevarech-david</t>
+        </is>
+      </c>
+      <c r="D56" s="8" t="n">
+        <v>184</v>
+      </c>
+      <c r="E56" s="8" t="inlineStr">
+        <is>
+          <t>Weekday / Shacharit / Pesukei Dezimra / Vayevarech David</t>
+        </is>
+      </c>
+      <c r="F56" s="19" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="25" customHeight="1">
+      <c r="A57" s="12" t="inlineStr">
+        <is>
+          <t>Shacharit</t>
+        </is>
+      </c>
+      <c r="B57" s="12" t="inlineStr">
+        <is>
+          <t>Yehi Chevod</t>
+        </is>
+      </c>
+      <c r="C57" s="12" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-ashkenaz-weekday-shacharit-pesukei-dezimra-yehi-chevod</t>
+        </is>
+      </c>
+      <c r="D57" s="12" t="n">
+        <v>176</v>
+      </c>
+      <c r="E57" s="12" t="inlineStr">
+        <is>
+          <t>Weekday / Shacharit / Pesukei Dezimra / Yehi Chevod</t>
+        </is>
+      </c>
+      <c r="F57" s="18" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="25" customHeight="1">
+      <c r="A58" s="8" t="inlineStr">
+        <is>
+          <t>Shacharit</t>
+        </is>
+      </c>
+      <c r="B58" s="8" t="inlineStr">
+        <is>
+          <t>Yishtabach</t>
+        </is>
+      </c>
+      <c r="C58" s="8" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-ashkenaz-weekday-shacharit-pesukei-dezimra-yishtabach</t>
+        </is>
+      </c>
+      <c r="D58" s="8" t="n">
+        <v>187</v>
+      </c>
+      <c r="E58" s="8" t="inlineStr">
+        <is>
+          <t>Weekday / Shacharit / Pesukei Dezimra / Yishtabach</t>
+        </is>
+      </c>
+      <c r="F58" s="19" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="25" customHeight="1">
+      <c r="A59" s="12" t="inlineStr">
+        <is>
+          <t>Shacharit</t>
+        </is>
+      </c>
+      <c r="B59" s="12" t="inlineStr">
+        <is>
+          <t>For Monday and Thursday</t>
+        </is>
+      </c>
+      <c r="C59" s="12" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-ashkenaz-weekday-shacharit-post-amidah-tachanun-for-monday-and-thursday</t>
+        </is>
+      </c>
+      <c r="D59" s="12" t="n">
+        <v>209</v>
+      </c>
+      <c r="E59" s="12" t="inlineStr">
+        <is>
+          <t>Weekday / Shacharit / Post Amidah / Tachanun / For Monday and Thursday</t>
+        </is>
+      </c>
+      <c r="F59" s="18" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="25" customHeight="1">
+      <c r="A60" s="8" t="inlineStr">
+        <is>
+          <t>Shacharit</t>
+        </is>
+      </c>
+      <c r="B60" s="8" t="inlineStr">
+        <is>
+          <t>God of Israel</t>
+        </is>
+      </c>
+      <c r="C60" s="8" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-ashkenaz-weekday-shacharit-post-amidah-tachanun-god-of-israel</t>
+        </is>
+      </c>
+      <c r="D60" s="8" t="n">
+        <v>211</v>
+      </c>
+      <c r="E60" s="8" t="inlineStr">
+        <is>
+          <t>Weekday / Shacharit / Post Amidah / Tachanun / God of Israel</t>
+        </is>
+      </c>
+      <c r="F60" s="19" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="25" customHeight="1">
+      <c r="A61" s="12" t="inlineStr">
+        <is>
+          <t>Shacharit</t>
+        </is>
+      </c>
+      <c r="B61" s="12" t="inlineStr">
+        <is>
+          <t>Half Kaddish</t>
+        </is>
+      </c>
+      <c r="C61" s="12" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-ashkenaz-weekday-shacharit-post-amidah-tachanun-half-kaddish</t>
+        </is>
+      </c>
+      <c r="D61" s="12" t="n">
+        <v>213</v>
+      </c>
+      <c r="E61" s="12" t="inlineStr">
+        <is>
+          <t>Weekday / Shacharit / Post Amidah / Tachanun / Half Kaddish</t>
+        </is>
+      </c>
+      <c r="F61" s="18" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="25" customHeight="1">
+      <c r="A62" s="8" t="inlineStr">
+        <is>
+          <t>Shacharit</t>
+        </is>
+      </c>
+      <c r="B62" s="8" t="inlineStr">
+        <is>
+          <t>Nefilat Apayim</t>
+        </is>
+      </c>
+      <c r="C62" s="8" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-ashkenaz-weekday-shacharit-post-amidah-tachanun-nefilat-apayim</t>
+        </is>
+      </c>
+      <c r="D62" s="8" t="n">
+        <v>210</v>
+      </c>
+      <c r="E62" s="8" t="inlineStr">
+        <is>
+          <t>Weekday / Shacharit / Post Amidah / Tachanun / Nefilat Apayim</t>
+        </is>
+      </c>
+      <c r="F62" s="19" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="25" customHeight="1">
+      <c r="A63" s="12" t="inlineStr">
+        <is>
+          <t>Shacharit</t>
+        </is>
+      </c>
+      <c r="B63" s="12" t="inlineStr">
+        <is>
+          <t>Shomer Yisrael</t>
+        </is>
+      </c>
+      <c r="C63" s="12" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-ashkenaz-weekday-shacharit-post-amidah-tachanun-shomer-yisrael</t>
+        </is>
+      </c>
+      <c r="D63" s="12" t="n">
+        <v>212</v>
+      </c>
+      <c r="E63" s="12" t="inlineStr">
+        <is>
+          <t>Weekday / Shacharit / Post Amidah / Tachanun / Shomer Yisrael</t>
+        </is>
+      </c>
+      <c r="F63" s="18" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="25" customHeight="1">
+      <c r="A64" s="8" t="inlineStr">
+        <is>
+          <t>Shacharit</t>
+        </is>
+      </c>
+      <c r="B64" s="8" t="inlineStr">
+        <is>
+          <t>Vidui and 13 Middot</t>
+        </is>
+      </c>
+      <c r="C64" s="8" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-ashkenaz-weekday-shacharit-post-amidah-vidui-and-13-middot</t>
+        </is>
+      </c>
+      <c r="D64" s="8" t="n">
+        <v>208</v>
+      </c>
+      <c r="E64" s="8" t="inlineStr">
+        <is>
+          <t>Weekday / Shacharit / Post Amidah / Vidui and 13 Middot</t>
+        </is>
+      </c>
+      <c r="F64" s="19" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="25" customHeight="1">
+      <c r="A65" s="12" t="inlineStr">
+        <is>
+          <t>Shacharit</t>
+        </is>
+      </c>
+      <c r="B65" s="12" t="inlineStr">
+        <is>
+          <t>Thirteen Principles</t>
+        </is>
+      </c>
+      <c r="C65" s="12" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-ashkenaz-weekday-shacharit-post-service-thirteen-principles</t>
+        </is>
+      </c>
+      <c r="D65" s="12" t="n">
+        <v>237</v>
+      </c>
+      <c r="E65" s="12" t="inlineStr">
+        <is>
+          <t>Weekday / Shacharit / Post Service / Thirteen Principles</t>
+        </is>
+      </c>
+      <c r="F65" s="18" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="25" customHeight="1">
+      <c r="A66" s="8" t="inlineStr">
+        <is>
+          <t>Shacharit</t>
+        </is>
+      </c>
+      <c r="B66" s="8" t="inlineStr">
+        <is>
+          <t>Adon Olam</t>
+        </is>
+      </c>
+      <c r="C66" s="8" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-ashkenaz-weekday-shacharit-preparatory-prayers-adon-olam</t>
+        </is>
+      </c>
+      <c r="D66" s="8" t="n">
+        <v>160</v>
+      </c>
+      <c r="E66" s="8" t="inlineStr">
+        <is>
+          <t>Weekday / Shacharit / Preparatory Prayers / Adon Olam</t>
+        </is>
+      </c>
+      <c r="F66" s="19" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="25" customHeight="1">
+      <c r="A67" s="12" t="inlineStr">
+        <is>
+          <t>Shacharit</t>
+        </is>
+      </c>
+      <c r="B67" s="12" t="inlineStr">
+        <is>
+          <t>Akedah</t>
+        </is>
+      </c>
+      <c r="C67" s="12" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-ashkenaz-weekday-shacharit-preparatory-prayers-akedah</t>
+        </is>
+      </c>
+      <c r="D67" s="12" t="n">
+        <v>162</v>
+      </c>
+      <c r="E67" s="12" t="inlineStr">
+        <is>
+          <t>Weekday / Shacharit / Preparatory Prayers / Akedah</t>
+        </is>
+      </c>
+      <c r="F67" s="18" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="25" customHeight="1">
+      <c r="A68" s="8" t="inlineStr">
+        <is>
+          <t>Shacharit</t>
+        </is>
+      </c>
+      <c r="B68" s="8" t="inlineStr">
+        <is>
+          <t>Asher Yatzar</t>
+        </is>
+      </c>
+      <c r="C68" s="8" t="inlineStr">
+        <is>
+          <t>asher-yatzar</t>
+        </is>
+      </c>
+      <c r="D68" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="E68" s="8" t="inlineStr">
+        <is>
+          <t>Weekday / Shacharit / Preparatory Prayers / Asher Yatzar</t>
+        </is>
+      </c>
+      <c r="F68" s="19" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="25" customHeight="1">
+      <c r="A69" s="12" t="inlineStr">
+        <is>
+          <t>Shacharit</t>
+        </is>
+      </c>
+      <c r="B69" s="12" t="inlineStr">
+        <is>
+          <t>Elokai Neshama</t>
+        </is>
+      </c>
+      <c r="C69" s="12" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-ashkenaz-weekday-shacharit-preparatory-prayers-elokai-neshama</t>
+        </is>
+      </c>
+      <c r="D69" s="12" t="n">
+        <v>156</v>
+      </c>
+      <c r="E69" s="12" t="inlineStr">
+        <is>
+          <t>Weekday / Shacharit / Preparatory Prayers / Elokai Neshama</t>
+        </is>
+      </c>
+      <c r="F69" s="18" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="25" customHeight="1">
+      <c r="A70" s="8" t="inlineStr">
+        <is>
+          <t>Shacharit</t>
+        </is>
+      </c>
+      <c r="B70" s="8" t="inlineStr">
+        <is>
+          <t>Baraita of Rabbi Yishmael</t>
+        </is>
+      </c>
+      <c r="C70" s="8" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-ashkenaz-weekday-shacharit-preparatory-prayers-korbanot-baraita-of-rabbi-yishmael</t>
+        </is>
+      </c>
+      <c r="D70" s="8" t="n">
+        <v>169</v>
+      </c>
+      <c r="E70" s="8" t="inlineStr">
+        <is>
+          <t>Weekday / Shacharit / Preparatory Prayers / Korbanot / Baraita of Rabbi Yishmael</t>
+        </is>
+      </c>
+      <c r="F70" s="19" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="25" customHeight="1">
+      <c r="A71" s="12" t="inlineStr">
+        <is>
+          <t>Shacharit</t>
+        </is>
+      </c>
+      <c r="B71" s="12" t="inlineStr">
+        <is>
+          <t>Kaddish DeRabbanan</t>
+        </is>
+      </c>
+      <c r="C71" s="12" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-ashkenaz-weekday-shacharit-preparatory-prayers-korbanot-kaddish-derabbanan</t>
+        </is>
+      </c>
+      <c r="D71" s="12" t="n">
+        <v>170</v>
+      </c>
+      <c r="E71" s="12" t="inlineStr">
+        <is>
+          <t>Weekday / Shacharit / Preparatory Prayers / Korbanot / Kaddish DeRabbanan</t>
+        </is>
+      </c>
+      <c r="F71" s="18" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="25" customHeight="1">
+      <c r="A72" s="8" t="inlineStr">
+        <is>
+          <t>Shacharit</t>
+        </is>
+      </c>
+      <c r="B72" s="8" t="inlineStr">
+        <is>
+          <t>Kiyor</t>
+        </is>
+      </c>
+      <c r="C72" s="8" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-ashkenaz-weekday-shacharit-preparatory-prayers-korbanot-kiyor</t>
+        </is>
+      </c>
+      <c r="D72" s="8" t="n">
+        <v>164</v>
+      </c>
+      <c r="E72" s="8" t="inlineStr">
+        <is>
+          <t>Weekday / Shacharit / Preparatory Prayers / Korbanot / Kiyor</t>
+        </is>
+      </c>
+      <c r="F72" s="19" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="25" customHeight="1">
+      <c r="A73" s="12" t="inlineStr">
+        <is>
+          <t>Shacharit</t>
+        </is>
+      </c>
+      <c r="B73" s="12" t="inlineStr">
+        <is>
+          <t>Korban HaTamid</t>
+        </is>
+      </c>
+      <c r="C73" s="12" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-ashkenaz-weekday-shacharit-preparatory-prayers-korbanot-korban-hatamid</t>
+        </is>
+      </c>
+      <c r="D73" s="12" t="n">
+        <v>166</v>
+      </c>
+      <c r="E73" s="12" t="inlineStr">
+        <is>
+          <t>Weekday / Shacharit / Preparatory Prayers / Korbanot / Korban HaTamid</t>
+        </is>
+      </c>
+      <c r="F73" s="18" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="25" customHeight="1">
+      <c r="A74" s="8" t="inlineStr">
+        <is>
+          <t>Shacharit</t>
+        </is>
+      </c>
+      <c r="B74" s="8" t="inlineStr">
+        <is>
+          <t>Laws of Sacrifices</t>
+        </is>
+      </c>
+      <c r="C74" s="8" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-ashkenaz-weekday-shacharit-preparatory-prayers-korbanot-laws-of-sacrifices</t>
+        </is>
+      </c>
+      <c r="D74" s="8" t="n">
+        <v>168</v>
+      </c>
+      <c r="E74" s="8" t="inlineStr">
+        <is>
+          <t>Weekday / Shacharit / Preparatory Prayers / Korbanot / Laws of Sacrifices</t>
+        </is>
+      </c>
+      <c r="F74" s="19" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="25" customHeight="1">
+      <c r="A75" s="12" t="inlineStr">
+        <is>
+          <t>Shacharit</t>
+        </is>
+      </c>
+      <c r="B75" s="12" t="inlineStr">
+        <is>
+          <t>Order of the Temple Service</t>
+        </is>
+      </c>
+      <c r="C75" s="12" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-ashkenaz-weekday-shacharit-preparatory-prayers-korbanot-order-of-the-temple-service</t>
+        </is>
+      </c>
+      <c r="D75" s="12" t="n">
+        <v>167</v>
+      </c>
+      <c r="E75" s="12" t="inlineStr">
+        <is>
+          <t>Weekday / Shacharit / Preparatory Prayers / Korbanot / Order of the Temple Service</t>
+        </is>
+      </c>
+      <c r="F75" s="18" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="25" customHeight="1">
+      <c r="A76" s="8" t="inlineStr">
+        <is>
+          <t>Shacharit</t>
+        </is>
+      </c>
+      <c r="B76" s="8" t="inlineStr">
+        <is>
+          <t>Terumat HaDeshen</t>
+        </is>
+      </c>
+      <c r="C76" s="8" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-ashkenaz-weekday-shacharit-preparatory-prayers-korbanot-terumat-hadeshen</t>
+        </is>
+      </c>
+      <c r="D76" s="8" t="n">
+        <v>165</v>
+      </c>
+      <c r="E76" s="8" t="inlineStr">
+        <is>
+          <t>Weekday / Shacharit / Preparatory Prayers / Korbanot / Terumat HaDeshen</t>
+        </is>
+      </c>
+      <c r="F76" s="19" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="25" customHeight="1">
+      <c r="A77" s="12" t="inlineStr">
+        <is>
+          <t>Shacharit</t>
+        </is>
+      </c>
+      <c r="B77" s="12" t="inlineStr">
+        <is>
+          <t>Ma Tovu</t>
+        </is>
+      </c>
+      <c r="C77" s="12" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-ashkenaz-weekday-shacharit-preparatory-prayers-ma-tovu</t>
+        </is>
+      </c>
+      <c r="D77" s="12" t="n">
+        <v>159</v>
+      </c>
+      <c r="E77" s="12" t="inlineStr">
+        <is>
+          <t>Weekday / Shacharit / Preparatory Prayers / Ma Tovu</t>
+        </is>
+      </c>
+      <c r="F77" s="18" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="25" customHeight="1">
+      <c r="A78" s="8" t="inlineStr">
+        <is>
+          <t>Shacharit</t>
+        </is>
+      </c>
+      <c r="B78" s="8" t="inlineStr">
+        <is>
+          <t>Modeh Ani</t>
+        </is>
+      </c>
+      <c r="C78" s="8" t="inlineStr">
+        <is>
+          <t>modeh-ani</t>
+        </is>
+      </c>
+      <c r="D78" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E78" s="8" t="inlineStr">
+        <is>
+          <t>Weekday / Shacharit / Preparatory Prayers / Modeh Ani</t>
+        </is>
+      </c>
+      <c r="F78" s="19" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="25" customHeight="1">
+      <c r="A79" s="12" t="inlineStr">
+        <is>
+          <t>Shacharit</t>
+        </is>
+      </c>
+      <c r="B79" s="12" t="inlineStr">
+        <is>
+          <t>Netilat Yadayim</t>
+        </is>
+      </c>
+      <c r="C79" s="12" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-ashkenaz-weekday-shacharit-preparatory-prayers-netilat-yadayim</t>
+        </is>
+      </c>
+      <c r="D79" s="12" t="n">
+        <v>155</v>
+      </c>
+      <c r="E79" s="12" t="inlineStr">
+        <is>
+          <t>Weekday / Shacharit / Preparatory Prayers / Netilat Yadayim</t>
+        </is>
+      </c>
+      <c r="F79" s="18" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="25" customHeight="1">
+      <c r="A80" s="8" t="inlineStr">
+        <is>
+          <t>Shacharit</t>
+        </is>
+      </c>
+      <c r="B80" s="8" t="inlineStr">
+        <is>
+          <t>Sovereignty of Heaven</t>
+        </is>
+      </c>
+      <c r="C80" s="8" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-ashkenaz-weekday-shacharit-preparatory-prayers-sovereignty-of-heaven</t>
+        </is>
+      </c>
+      <c r="D80" s="8" t="n">
+        <v>163</v>
+      </c>
+      <c r="E80" s="8" t="inlineStr">
+        <is>
+          <t>Weekday / Shacharit / Preparatory Prayers / Sovereignty of Heaven</t>
+        </is>
+      </c>
+      <c r="F80" s="19" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="25" customHeight="1">
+      <c r="A81" s="12" t="inlineStr">
+        <is>
+          <t>Shacharit</t>
+        </is>
+      </c>
+      <c r="B81" s="12" t="inlineStr">
+        <is>
+          <t>Torah Blessings</t>
+        </is>
+      </c>
+      <c r="C81" s="12" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-ashkenaz-weekday-shacharit-preparatory-prayers-torah-blessings</t>
+        </is>
+      </c>
+      <c r="D81" s="12" t="n">
+        <v>158</v>
+      </c>
+      <c r="E81" s="12" t="inlineStr">
+        <is>
+          <t>Weekday / Shacharit / Preparatory Prayers / Torah Blessings</t>
+        </is>
+      </c>
+      <c r="F81" s="18" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="25" customHeight="1">
+      <c r="A82" s="8" t="inlineStr">
+        <is>
+          <t>Shacharit</t>
+        </is>
+      </c>
+      <c r="B82" s="8" t="inlineStr">
+        <is>
+          <t>Tzitzit</t>
+        </is>
+      </c>
+      <c r="C82" s="8" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-ashkenaz-weekday-shacharit-preparatory-prayers-tzitzit</t>
+        </is>
+      </c>
+      <c r="D82" s="8" t="n">
+        <v>157</v>
+      </c>
+      <c r="E82" s="8" t="inlineStr">
+        <is>
+          <t>Weekday / Shacharit / Preparatory Prayers / Tzitzit</t>
+        </is>
+      </c>
+      <c r="F82" s="19" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="25" customHeight="1">
+      <c r="A83" s="12" t="inlineStr">
+        <is>
+          <t>Shacharit</t>
+        </is>
+      </c>
+      <c r="B83" s="12" t="inlineStr">
+        <is>
+          <t>Yigdal</t>
+        </is>
+      </c>
+      <c r="C83" s="12" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-ashkenaz-weekday-shacharit-preparatory-prayers-yigdal</t>
+        </is>
+      </c>
+      <c r="D83" s="12" t="n">
+        <v>161</v>
+      </c>
+      <c r="E83" s="12" t="inlineStr">
+        <is>
+          <t>Weekday / Shacharit / Preparatory Prayers / Yigdal</t>
+        </is>
+      </c>
+      <c r="F83" s="18" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="25" customHeight="1">
+      <c r="A84" s="8" t="inlineStr">
+        <is>
+          <t>Shacharit</t>
+        </is>
+      </c>
+      <c r="B84" s="8" t="inlineStr">
+        <is>
+          <t>Birkat HaTorah</t>
+        </is>
+      </c>
+      <c r="C84" s="8" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-ashkenaz-weekday-shacharit-torah-reading-reading-from-sefer-birkat-hatorah</t>
+        </is>
+      </c>
+      <c r="D84" s="8" t="n">
+        <v>220</v>
+      </c>
+      <c r="E84" s="8" t="inlineStr">
+        <is>
+          <t>Weekday / Shacharit / Torah Reading / Reading from Sefer / Birkat HaTorah</t>
+        </is>
+      </c>
+      <c r="F84" s="19" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="25" customHeight="1">
+      <c r="A85" s="12" t="inlineStr">
+        <is>
+          <t>Shacharit</t>
+        </is>
+      </c>
+      <c r="B85" s="12" t="inlineStr">
+        <is>
+          <t>Half Kaddish</t>
+        </is>
+      </c>
+      <c r="C85" s="12" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-ashkenaz-weekday-shacharit-torah-reading-reading-from-sefer-half-kaddish</t>
+        </is>
+      </c>
+      <c r="D85" s="12" t="n">
+        <v>221</v>
+      </c>
+      <c r="E85" s="12" t="inlineStr">
+        <is>
+          <t>Weekday / Shacharit / Torah Reading / Reading from Sefer / Half Kaddish</t>
+        </is>
+      </c>
+      <c r="F85" s="18" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="25" customHeight="1">
+      <c r="A86" s="8" t="inlineStr">
+        <is>
+          <t>Shacharit</t>
+        </is>
+      </c>
+      <c r="B86" s="8" t="inlineStr">
+        <is>
+          <t>Av Harachamim</t>
+        </is>
+      </c>
+      <c r="C86" s="8" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-ashkenaz-weekday-shacharit-torah-reading-removing-the-torah-from-ark-av-harachamim</t>
+        </is>
+      </c>
+      <c r="D86" s="8" t="n">
+        <v>218</v>
+      </c>
+      <c r="E86" s="8" t="inlineStr">
+        <is>
+          <t>Weekday / Shacharit / Torah Reading / Removing the Torah from Ark / Av Harachamim</t>
+        </is>
+      </c>
+      <c r="F86" s="19" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="25" customHeight="1">
+      <c r="A87" s="12" t="inlineStr">
+        <is>
+          <t>Shacharit</t>
+        </is>
+      </c>
+      <c r="B87" s="12" t="inlineStr">
+        <is>
+          <t>Berich Shmei</t>
+        </is>
+      </c>
+      <c r="C87" s="12" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-ashkenaz-weekday-shacharit-torah-reading-removing-the-torah-from-ark-berich-shmei</t>
+        </is>
+      </c>
+      <c r="D87" s="12" t="n">
+        <v>216</v>
+      </c>
+      <c r="E87" s="12" t="inlineStr">
+        <is>
+          <t>Weekday / Shacharit / Torah Reading / Removing the Torah from Ark / Berich Shmei</t>
+        </is>
+      </c>
+      <c r="F87" s="18" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="25" customHeight="1">
+      <c r="A88" s="8" t="inlineStr">
+        <is>
+          <t>Shacharit</t>
+        </is>
+      </c>
+      <c r="B88" s="8" t="inlineStr">
+        <is>
+          <t>El Erech Appayim</t>
+        </is>
+      </c>
+      <c r="C88" s="8" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-ashkenaz-weekday-shacharit-torah-reading-removing-the-torah-from-ark-el-erech-appayim</t>
+        </is>
+      </c>
+      <c r="D88" s="8" t="n">
+        <v>214</v>
+      </c>
+      <c r="E88" s="8" t="inlineStr">
+        <is>
+          <t>Weekday / Shacharit / Torah Reading / Removing the Torah from Ark / El Erech Appayim</t>
+        </is>
+      </c>
+      <c r="F88" s="19" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="25" customHeight="1">
+      <c r="A89" s="12" t="inlineStr">
+        <is>
+          <t>Shacharit</t>
+        </is>
+      </c>
+      <c r="B89" s="12" t="inlineStr">
+        <is>
+          <t>Lekha Hashem</t>
+        </is>
+      </c>
+      <c r="C89" s="12" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-ashkenaz-weekday-shacharit-torah-reading-removing-the-torah-from-ark-lekha-hashem</t>
+        </is>
+      </c>
+      <c r="D89" s="12" t="n">
+        <v>217</v>
+      </c>
+      <c r="E89" s="12" t="inlineStr">
+        <is>
+          <t>Weekday / Shacharit / Torah Reading / Removing the Torah from Ark / Lekha Hashem</t>
+        </is>
+      </c>
+      <c r="F89" s="18" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="25" customHeight="1">
+      <c r="A90" s="8" t="inlineStr">
+        <is>
+          <t>Shacharit</t>
+        </is>
+      </c>
+      <c r="B90" s="8" t="inlineStr">
+        <is>
+          <t>Vayehi Binsoa</t>
+        </is>
+      </c>
+      <c r="C90" s="8" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-ashkenaz-weekday-shacharit-torah-reading-removing-the-torah-from-ark-vayehi-binsoa</t>
+        </is>
+      </c>
+      <c r="D90" s="8" t="n">
+        <v>215</v>
+      </c>
+      <c r="E90" s="8" t="inlineStr">
+        <is>
+          <t>Weekday / Shacharit / Torah Reading / Removing the Torah from Ark / Vayehi Binsoa</t>
+        </is>
+      </c>
+      <c r="F90" s="19" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="25" customHeight="1">
+      <c r="A91" s="12" t="inlineStr">
+        <is>
+          <t>Shacharit</t>
+        </is>
+      </c>
+      <c r="B91" s="12" t="inlineStr">
+        <is>
+          <t>Vetigaleh Veteraeh</t>
+        </is>
+      </c>
+      <c r="C91" s="12" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-ashkenaz-weekday-shacharit-torah-reading-removing-the-torah-from-ark-vetigaleh-veteraeh</t>
+        </is>
+      </c>
+      <c r="D91" s="12" t="n">
+        <v>219</v>
+      </c>
+      <c r="E91" s="12" t="inlineStr">
+        <is>
+          <t>Weekday / Shacharit / Torah Reading / Removing the Torah from Ark / Vetigaleh Veteraeh</t>
+        </is>
+      </c>
+      <c r="F91" s="18" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="25" customHeight="1">
+      <c r="A92" s="8" t="inlineStr">
+        <is>
+          <t>Shacharit</t>
+        </is>
+      </c>
+      <c r="B92" s="8" t="inlineStr">
+        <is>
+          <t>LeDavid Mizmor</t>
+        </is>
+      </c>
+      <c r="C92" s="8" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-ashkenaz-weekday-shacharit-torah-reading-returning-sefer-to-aron-ledavid-mizmor</t>
+        </is>
+      </c>
+      <c r="D92" s="8" t="n">
+        <v>223</v>
+      </c>
+      <c r="E92" s="8" t="inlineStr">
+        <is>
+          <t>Weekday / Shacharit / Torah Reading / Returning Sefer to Aron / LeDavid Mizmor</t>
+        </is>
+      </c>
+      <c r="F92" s="19" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="25" customHeight="1">
+      <c r="A93" s="12" t="inlineStr">
+        <is>
+          <t>Shacharit</t>
+        </is>
+      </c>
+      <c r="B93" s="12" t="inlineStr">
+        <is>
+          <t>Uvenucho Yomar</t>
+        </is>
+      </c>
+      <c r="C93" s="12" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-ashkenaz-weekday-shacharit-torah-reading-returning-sefer-to-aron-uvenucho-yomar</t>
+        </is>
+      </c>
+      <c r="D93" s="12" t="n">
+        <v>224</v>
+      </c>
+      <c r="E93" s="12" t="inlineStr">
+        <is>
+          <t>Weekday / Shacharit / Torah Reading / Returning Sefer to Aron / Uvenucho Yomar</t>
+        </is>
+      </c>
+      <c r="F93" s="18" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="25" customHeight="1">
+      <c r="A94" s="8" t="inlineStr">
+        <is>
+          <t>Shacharit</t>
+        </is>
+      </c>
+      <c r="B94" s="8" t="inlineStr">
+        <is>
+          <t>Yehalelu</t>
+        </is>
+      </c>
+      <c r="C94" s="8" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-ashkenaz-weekday-shacharit-torah-reading-returning-sefer-to-aron-yehalelu</t>
+        </is>
+      </c>
+      <c r="D94" s="8" t="n">
+        <v>222</v>
+      </c>
+      <c r="E94" s="8" t="inlineStr">
+        <is>
+          <t>Weekday / Shacharit / Torah Reading / Returning Sefer to Aron / Yehalelu</t>
+        </is>
+      </c>
+      <c r="F94" s="19" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="25" customHeight="1">
+      <c r="A95" s="12" t="inlineStr">
+        <is>
+          <t>Shacharit</t>
+        </is>
+      </c>
+      <c r="B95" s="12" t="inlineStr">
+        <is>
+          <t>Aleinu</t>
+        </is>
+      </c>
+      <c r="C95" s="12" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-sefard-weekday-shacharit-aleinu</t>
+        </is>
+      </c>
+      <c r="D95" s="12" t="n">
+        <v>344</v>
+      </c>
+      <c r="E95" s="12" t="inlineStr">
+        <is>
+          <t>Weekday Shacharit / Aleinu</t>
+        </is>
+      </c>
+      <c r="F95" s="18" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="25" customHeight="1">
+      <c r="A96" s="8" t="inlineStr">
+        <is>
+          <t>Shacharit</t>
+        </is>
+      </c>
+      <c r="B96" s="8" t="inlineStr">
+        <is>
+          <t>Ashrei</t>
+        </is>
+      </c>
+      <c r="C96" s="8" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-sefard-weekday-shacharit-ashrei</t>
+        </is>
+      </c>
+      <c r="D96" s="8" t="n">
+        <v>339</v>
+      </c>
+      <c r="E96" s="8" t="inlineStr">
+        <is>
+          <t>Weekday Shacharit / Ashrei</t>
+        </is>
+      </c>
+      <c r="F96" s="19" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="25" customHeight="1">
+      <c r="A97" s="12" t="inlineStr">
+        <is>
+          <t>Shacharit</t>
+        </is>
+      </c>
+      <c r="B97" s="12" t="inlineStr">
+        <is>
+          <t>Avinu Malkeinu</t>
+        </is>
+      </c>
+      <c r="C97" s="12" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-sefard-weekday-shacharit-avinu-malkeinu</t>
+        </is>
+      </c>
+      <c r="D97" s="12" t="n">
+        <v>337</v>
+      </c>
+      <c r="E97" s="12" t="inlineStr">
+        <is>
+          <t>Weekday Shacharit / Avinu Malkeinu</t>
+        </is>
+      </c>
+      <c r="F97" s="18" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="25" customHeight="1">
+      <c r="A98" s="8" t="inlineStr">
+        <is>
+          <t>Shacharit</t>
+        </is>
+      </c>
+      <c r="B98" s="8" t="inlineStr">
+        <is>
+          <t>B'raita d'Rabi Yishmael</t>
+        </is>
+      </c>
+      <c r="C98" s="8" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-sefard-weekday-shacharit-b-raita-d-rabi-yishmael</t>
+        </is>
+      </c>
+      <c r="D98" s="8" t="n">
+        <v>333</v>
+      </c>
+      <c r="E98" s="8" t="inlineStr">
+        <is>
+          <t>Weekday Shacharit / B'raita d'Rabi Yishmael</t>
+        </is>
+      </c>
+      <c r="F98" s="19" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="25" customHeight="1">
+      <c r="A99" s="12" t="inlineStr">
+        <is>
+          <t>Shacharit</t>
+        </is>
+      </c>
+      <c r="B99" s="12" t="inlineStr">
+        <is>
+          <t>Barchi Nafshi</t>
+        </is>
+      </c>
+      <c r="C99" s="12" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-sefard-weekday-shacharit-barchi-nafshi</t>
+        </is>
+      </c>
+      <c r="D99" s="12" t="n">
+        <v>341</v>
+      </c>
+      <c r="E99" s="12" t="inlineStr">
+        <is>
+          <t>Weekday Shacharit / Barchi Nafshi</t>
+        </is>
+      </c>
+      <c r="F99" s="18" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="25" customHeight="1">
+      <c r="A100" s="8" t="inlineStr">
+        <is>
+          <t>Shacharit</t>
+        </is>
+      </c>
+      <c r="B100" s="8" t="inlineStr">
+        <is>
+          <t>Blessings on Torah</t>
+        </is>
+      </c>
+      <c r="C100" s="8" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-sefard-weekday-shacharit-blessings-on-torah</t>
+        </is>
+      </c>
+      <c r="D100" s="8" t="n">
+        <v>330</v>
+      </c>
+      <c r="E100" s="8" t="inlineStr">
+        <is>
+          <t>Weekday Shacharit / Blessings on Torah</t>
+        </is>
+      </c>
+      <c r="F100" s="19" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="25" customHeight="1">
+      <c r="A101" s="12" t="inlineStr">
+        <is>
+          <t>Shacharit</t>
+        </is>
+      </c>
+      <c r="B101" s="12" t="inlineStr">
+        <is>
+          <t>For Monday &amp; Thursday</t>
+        </is>
+      </c>
+      <c r="C101" s="12" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-sefard-weekday-shacharit-for-monday-thursday</t>
+        </is>
+      </c>
+      <c r="D101" s="12" t="n">
+        <v>338</v>
+      </c>
+      <c r="E101" s="12" t="inlineStr">
+        <is>
+          <t>Weekday Shacharit / For Monday &amp; Thursday</t>
+        </is>
+      </c>
+      <c r="F101" s="18" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="25" customHeight="1">
+      <c r="A102" s="8" t="inlineStr">
+        <is>
+          <t>Shacharit</t>
+        </is>
+      </c>
+      <c r="B102" s="8" t="inlineStr">
+        <is>
+          <t>Hodu</t>
+        </is>
+      </c>
+      <c r="C102" s="8" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-sefard-weekday-shacharit-hodu</t>
+        </is>
+      </c>
+      <c r="D102" s="8" t="n">
+        <v>334</v>
+      </c>
+      <c r="E102" s="8" t="inlineStr">
+        <is>
+          <t>Weekday Shacharit / Hodu</t>
+        </is>
+      </c>
+      <c r="F102" s="19" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="25" customHeight="1">
+      <c r="A103" s="12" t="inlineStr">
+        <is>
+          <t>Shacharit</t>
+        </is>
+      </c>
+      <c r="B103" s="12" t="inlineStr">
+        <is>
+          <t>Kaveh</t>
+        </is>
+      </c>
+      <c r="C103" s="12" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-sefard-weekday-shacharit-kaveh</t>
+        </is>
+      </c>
+      <c r="D103" s="12" t="n">
+        <v>343</v>
+      </c>
+      <c r="E103" s="12" t="inlineStr">
+        <is>
+          <t>Weekday Shacharit / Kaveh</t>
+        </is>
+      </c>
+      <c r="F103" s="18" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="25" customHeight="1">
+      <c r="A104" s="8" t="inlineStr">
+        <is>
+          <t>Shacharit</t>
+        </is>
+      </c>
+      <c r="B104" s="8" t="inlineStr">
+        <is>
+          <t>Korbanot</t>
+        </is>
+      </c>
+      <c r="C104" s="8" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-sefard-weekday-shacharit-korbanot</t>
+        </is>
+      </c>
+      <c r="D104" s="8" t="n">
+        <v>332</v>
+      </c>
+      <c r="E104" s="8" t="inlineStr">
+        <is>
+          <t>Weekday Shacharit / Korbanot</t>
+        </is>
+      </c>
+      <c r="F104" s="19" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="25" customHeight="1">
+      <c r="A105" s="12" t="inlineStr">
+        <is>
+          <t>Shacharit</t>
+        </is>
+      </c>
+      <c r="B105" s="12" t="inlineStr">
+        <is>
+          <t>L'David Hashem</t>
+        </is>
+      </c>
+      <c r="C105" s="12" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-sefard-weekday-shacharit-l-david-hashem</t>
+        </is>
+      </c>
+      <c r="D105" s="12" t="n">
+        <v>342</v>
+      </c>
+      <c r="E105" s="12" t="inlineStr">
+        <is>
+          <t>Weekday Shacharit / L'David Hashem</t>
+        </is>
+      </c>
+      <c r="F105" s="18" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="25" customHeight="1">
+      <c r="A106" s="8" t="inlineStr">
+        <is>
+          <t>Shacharit</t>
+        </is>
+      </c>
+      <c r="B106" s="8" t="inlineStr">
+        <is>
+          <t>Morning Blessings</t>
+        </is>
+      </c>
+      <c r="C106" s="8" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-sefard-weekday-shacharit-morning-blessings</t>
+        </is>
+      </c>
+      <c r="D106" s="8" t="n">
+        <v>329</v>
+      </c>
+      <c r="E106" s="8" t="inlineStr">
+        <is>
+          <t>Weekday Shacharit / Morning Blessings</t>
+        </is>
+      </c>
+      <c r="F106" s="19" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="25" customHeight="1">
+      <c r="A107" s="12" t="inlineStr">
+        <is>
+          <t>Shacharit</t>
+        </is>
+      </c>
+      <c r="B107" s="12" t="inlineStr">
+        <is>
+          <t>Morning Prayer</t>
+        </is>
+      </c>
+      <c r="C107" s="12" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-sefard-weekday-shacharit-morning-prayer</t>
+        </is>
+      </c>
+      <c r="D107" s="12" t="n">
+        <v>331</v>
+      </c>
+      <c r="E107" s="12" t="inlineStr">
+        <is>
+          <t>Weekday Shacharit / Morning Prayer</t>
+        </is>
+      </c>
+      <c r="F107" s="18" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="25" customHeight="1">
+      <c r="A108" s="8" t="inlineStr">
+        <is>
+          <t>Shacharit</t>
+        </is>
+      </c>
+      <c r="B108" s="8" t="inlineStr">
+        <is>
+          <t>Song of the Day</t>
+        </is>
+      </c>
+      <c r="C108" s="8" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-sefard-weekday-shacharit-song-of-the-day</t>
+        </is>
+      </c>
+      <c r="D108" s="8" t="n">
+        <v>340</v>
+      </c>
+      <c r="E108" s="8" t="inlineStr">
+        <is>
+          <t>Weekday Shacharit / Song of the Day</t>
+        </is>
+      </c>
+      <c r="F108" s="19" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="25" customHeight="1">
+      <c r="A109" s="12" t="inlineStr">
+        <is>
+          <t>Shacharit</t>
+        </is>
+      </c>
+      <c r="B109" s="12" t="inlineStr">
+        <is>
+          <t>Tachanun</t>
+        </is>
+      </c>
+      <c r="C109" s="12" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-sefard-weekday-shacharit-tachanun</t>
+        </is>
+      </c>
+      <c r="D109" s="12" t="n">
+        <v>336</v>
+      </c>
+      <c r="E109" s="12" t="inlineStr">
+        <is>
+          <t>Weekday Shacharit / Tachanun</t>
+        </is>
+      </c>
+      <c r="F109" s="18" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="25" customHeight="1">
+      <c r="A110" s="8" t="inlineStr">
+        <is>
+          <t>Shacharit</t>
+        </is>
+      </c>
+      <c r="B110" s="8" t="inlineStr">
+        <is>
+          <t>Yishtabach</t>
+        </is>
+      </c>
+      <c r="C110" s="8" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-sefard-weekday-shacharit-yishtabach</t>
+        </is>
+      </c>
+      <c r="D110" s="8" t="n">
+        <v>335</v>
+      </c>
+      <c r="E110" s="8" t="inlineStr">
+        <is>
+          <t>Weekday Shacharit / Yishtabach</t>
+        </is>
+      </c>
+      <c r="F110" s="19" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="25" customHeight="1">
+      <c r="A111" s="12" t="inlineStr">
         <is>
           <t>Mincha</t>
         </is>
       </c>
-      <c r="C6" s="17" t="inlineStr">
-        <is>
-          <t>Ashkenaz</t>
-        </is>
-      </c>
-      <c r="D6" s="17" t="inlineStr">
-        <is>
-          <t>No Hebrew candidate is ready for approval.</t>
-        </is>
-      </c>
-      <c r="E6" s="17" t="inlineStr">
-        <is>
-          <t>Siddur Ashkenaz, Weekday Minchah. Service collection, not a single prayer. Source snapshot not yet pinned; section-level source plan required.</t>
-        </is>
-      </c>
-      <c r="F6" s="17" t="inlineStr"/>
-    </row>
-    <row r="7" ht="60" customHeight="1">
-      <c r="A7" s="17" t="inlineStr">
-        <is>
-          <t>Section review required</t>
-        </is>
-      </c>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B111" s="12" t="inlineStr">
+        <is>
+          <t>Aleinu</t>
+        </is>
+      </c>
+      <c r="C111" s="12" t="inlineStr">
+        <is>
+          <t>sefaria-machzor-rosh-hashanah-ashkenaz-mincha-aleinu</t>
+        </is>
+      </c>
+      <c r="D111" s="12" t="n">
+        <v>430</v>
+      </c>
+      <c r="E111" s="12" t="inlineStr">
+        <is>
+          <t>Mincha / Aleinu</t>
+        </is>
+      </c>
+      <c r="F111" s="18" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="25" customHeight="1">
+      <c r="A112" s="8" t="inlineStr">
+        <is>
+          <t>Mincha</t>
+        </is>
+      </c>
+      <c r="B112" s="8" t="inlineStr">
+        <is>
+          <t>Mourner's Kaddish</t>
+        </is>
+      </c>
+      <c r="C112" s="8" t="inlineStr">
+        <is>
+          <t>sefaria-machzor-rosh-hashanah-ashkenaz-mincha-mourner-s-kaddish</t>
+        </is>
+      </c>
+      <c r="D112" s="8" t="n">
+        <v>431</v>
+      </c>
+      <c r="E112" s="8" t="inlineStr">
+        <is>
+          <t>Mincha / Mourner's Kaddish</t>
+        </is>
+      </c>
+      <c r="F112" s="19" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="25" customHeight="1">
+      <c r="A113" s="12" t="inlineStr">
+        <is>
+          <t>Mincha</t>
+        </is>
+      </c>
+      <c r="B113" s="12" t="inlineStr">
+        <is>
+          <t>Mourner's Kaddish</t>
+        </is>
+      </c>
+      <c r="C113" s="12" t="inlineStr">
+        <is>
+          <t>sefaria-machzor-rosh-hashanah-ashkenaz-linear-mincha-mourner-s-kaddish</t>
+        </is>
+      </c>
+      <c r="D113" s="12" t="n">
+        <v>439</v>
+      </c>
+      <c r="E113" s="12" t="inlineStr">
+        <is>
+          <t>Mincha / Mourner's Kaddish</t>
+        </is>
+      </c>
+      <c r="F113" s="18" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="25" customHeight="1">
+      <c r="A114" s="8" t="inlineStr">
+        <is>
+          <t>Mincha</t>
+        </is>
+      </c>
+      <c r="B114" s="8" t="inlineStr">
+        <is>
+          <t>Mourner's Kaddish</t>
+        </is>
+      </c>
+      <c r="C114" s="8" t="inlineStr">
+        <is>
+          <t>sefaria-machzor-rosh-hashanah-ashkenaz-mincha-for-erev-rosh-hashana-mourner-s-kaddish</t>
+        </is>
+      </c>
+      <c r="D114" s="8" t="n">
+        <v>417</v>
+      </c>
+      <c r="E114" s="8" t="inlineStr">
+        <is>
+          <t>Mincha for Erev Rosh Hashana / Mourner's Kaddish</t>
+        </is>
+      </c>
+      <c r="F114" s="19" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="25" customHeight="1">
+      <c r="A115" s="12" t="inlineStr">
+        <is>
+          <t>Mincha</t>
+        </is>
+      </c>
+      <c r="B115" s="12" t="inlineStr">
+        <is>
+          <t>Mourner's Kaddish</t>
+        </is>
+      </c>
+      <c r="C115" s="12" t="inlineStr">
+        <is>
+          <t>sefaria-machzor-rosh-hashanah-ashkenaz-linear-mincha-for-erev-rosh-hashana-mourner-s-kaddish</t>
+        </is>
+      </c>
+      <c r="D115" s="12" t="n">
+        <v>432</v>
+      </c>
+      <c r="E115" s="12" t="inlineStr">
+        <is>
+          <t>Mincha for Erev Rosh Hashana / Mourner's Kaddish</t>
+        </is>
+      </c>
+      <c r="F115" s="18" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="25" customHeight="1">
+      <c r="A116" s="8" t="inlineStr">
+        <is>
+          <t>Mincha</t>
+        </is>
+      </c>
+      <c r="B116" s="8" t="inlineStr">
+        <is>
+          <t>Aleinu</t>
+        </is>
+      </c>
+      <c r="C116" s="8" t="inlineStr">
+        <is>
+          <t>sefaria-shabbat-siddur-sefard-linear-mincha-service-for-erev-shabbos-aleinu</t>
+        </is>
+      </c>
+      <c r="D116" s="8" t="n">
+        <v>368</v>
+      </c>
+      <c r="E116" s="8" t="inlineStr">
+        <is>
+          <t>Mincha Service for Erev Shabbos / Aleinu</t>
+        </is>
+      </c>
+      <c r="F116" s="19" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="25" customHeight="1">
+      <c r="A117" s="12" t="inlineStr">
+        <is>
+          <t>Mincha</t>
+        </is>
+      </c>
+      <c r="B117" s="12" t="inlineStr">
+        <is>
+          <t>Psalm 107</t>
+        </is>
+      </c>
+      <c r="C117" s="12" t="inlineStr">
+        <is>
+          <t>sefaria-shabbat-siddur-sefard-linear-mincha-service-for-erev-shabbos-psalm-107</t>
+        </is>
+      </c>
+      <c r="D117" s="12" t="n">
+        <v>367</v>
+      </c>
+      <c r="E117" s="12" t="inlineStr">
+        <is>
+          <t>Mincha Service for Erev Shabbos / Psalm 107</t>
+        </is>
+      </c>
+      <c r="F117" s="18" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="25" customHeight="1">
+      <c r="A118" s="8" t="inlineStr">
+        <is>
+          <t>Mincha</t>
+        </is>
+      </c>
+      <c r="B118" s="8" t="inlineStr">
+        <is>
+          <t>Aleinu</t>
+        </is>
+      </c>
+      <c r="C118" s="8" t="inlineStr">
+        <is>
+          <t>sefaria-shabbat-siddur-sefard-linear-mincha-service-for-shabbos-and-yom-tov-aleinu</t>
+        </is>
+      </c>
+      <c r="D118" s="8" t="n">
+        <v>388</v>
+      </c>
+      <c r="E118" s="8" t="inlineStr">
+        <is>
+          <t>Mincha Service for Shabbos and Yom Tov / Aleinu</t>
+        </is>
+      </c>
+      <c r="F118" s="19" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="25" customHeight="1">
+      <c r="A119" s="12" t="inlineStr">
+        <is>
+          <t>Mincha</t>
+        </is>
+      </c>
+      <c r="B119" s="12" t="inlineStr">
+        <is>
+          <t>Ashrei</t>
+        </is>
+      </c>
+      <c r="C119" s="12" t="inlineStr">
+        <is>
+          <t>sefaria-shabbat-siddur-sefard-linear-mincha-service-for-shabbos-and-yom-tov-ashrei</t>
+        </is>
+      </c>
+      <c r="D119" s="12" t="n">
+        <v>387</v>
+      </c>
+      <c r="E119" s="12" t="inlineStr">
+        <is>
+          <t>Mincha Service for Shabbos and Yom Tov / Ashrei</t>
+        </is>
+      </c>
+      <c r="F119" s="18" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="25" customHeight="1">
+      <c r="A120" s="8" t="inlineStr">
+        <is>
+          <t>Mincha</t>
+        </is>
+      </c>
+      <c r="B120" s="8" t="inlineStr">
+        <is>
+          <t>Against Enemies</t>
+        </is>
+      </c>
+      <c r="C120" s="8" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-ashkenaz-weekday-minchah-amida-against-enemies</t>
+        </is>
+      </c>
+      <c r="D120" s="8" t="n">
+        <v>245</v>
+      </c>
+      <c r="E120" s="8" t="inlineStr">
+        <is>
+          <t>Weekday / Minchah / Amida / Against Enemies</t>
+        </is>
+      </c>
+      <c r="F120" s="19" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="25" customHeight="1">
+      <c r="A121" s="12" t="inlineStr">
+        <is>
+          <t>Mincha</t>
+        </is>
+      </c>
+      <c r="B121" s="12" t="inlineStr">
+        <is>
+          <t>Birkat Kohanim</t>
+        </is>
+      </c>
+      <c r="C121" s="12" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-ashkenaz-weekday-minchah-amida-birkat-kohanim</t>
+        </is>
+      </c>
+      <c r="D121" s="12" t="n">
+        <v>251</v>
+      </c>
+      <c r="E121" s="12" t="inlineStr">
+        <is>
+          <t>Weekday / Minchah / Amida / Birkat Kohanim</t>
+        </is>
+      </c>
+      <c r="F121" s="18" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="25" customHeight="1">
+      <c r="A122" s="8" t="inlineStr">
+        <is>
+          <t>Mincha</t>
+        </is>
+      </c>
+      <c r="B122" s="8" t="inlineStr">
+        <is>
+          <t>Concluding Passage</t>
+        </is>
+      </c>
+      <c r="C122" s="8" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-ashkenaz-weekday-minchah-amida-concluding-passage</t>
+        </is>
+      </c>
+      <c r="D122" s="8" t="n">
+        <v>252</v>
+      </c>
+      <c r="E122" s="8" t="inlineStr">
+        <is>
+          <t>Weekday / Minchah / Amida / Concluding Passage</t>
+        </is>
+      </c>
+      <c r="F122" s="19" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="25" customHeight="1">
+      <c r="A123" s="12" t="inlineStr">
+        <is>
+          <t>Mincha</t>
+        </is>
+      </c>
+      <c r="B123" s="12" t="inlineStr">
+        <is>
+          <t>Forgiveness</t>
+        </is>
+      </c>
+      <c r="C123" s="12" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-ashkenaz-weekday-minchah-amida-forgiveness</t>
+        </is>
+      </c>
+      <c r="D123" s="12" t="n">
+        <v>242</v>
+      </c>
+      <c r="E123" s="12" t="inlineStr">
+        <is>
+          <t>Weekday / Minchah / Amida / Forgiveness</t>
+        </is>
+      </c>
+      <c r="F123" s="18" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="25" customHeight="1">
+      <c r="A124" s="8" t="inlineStr">
+        <is>
+          <t>Mincha</t>
+        </is>
+      </c>
+      <c r="B124" s="8" t="inlineStr">
+        <is>
+          <t>Gathering the Exiles</t>
+        </is>
+      </c>
+      <c r="C124" s="8" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-ashkenaz-weekday-minchah-amida-gathering-the-exiles</t>
+        </is>
+      </c>
+      <c r="D124" s="8" t="n">
+        <v>244</v>
+      </c>
+      <c r="E124" s="8" t="inlineStr">
+        <is>
+          <t>Weekday / Minchah / Amida / Gathering the Exiles</t>
+        </is>
+      </c>
+      <c r="F124" s="19" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="25" customHeight="1">
+      <c r="A125" s="12" t="inlineStr">
+        <is>
+          <t>Mincha</t>
+        </is>
+      </c>
+      <c r="B125" s="12" t="inlineStr">
+        <is>
+          <t>Healing</t>
+        </is>
+      </c>
+      <c r="C125" s="12" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-ashkenaz-weekday-minchah-amida-healing</t>
+        </is>
+      </c>
+      <c r="D125" s="12" t="n">
+        <v>243</v>
+      </c>
+      <c r="E125" s="12" t="inlineStr">
+        <is>
+          <t>Weekday / Minchah / Amida / Healing</t>
+        </is>
+      </c>
+      <c r="F125" s="18" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="25" customHeight="1">
+      <c r="A126" s="8" t="inlineStr">
+        <is>
+          <t>Mincha</t>
+        </is>
+      </c>
+      <c r="B126" s="8" t="inlineStr">
+        <is>
+          <t>Keduasha</t>
+        </is>
+      </c>
+      <c r="C126" s="8" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-ashkenaz-weekday-minchah-amida-keduasha</t>
+        </is>
+      </c>
+      <c r="D126" s="8" t="n">
+        <v>239</v>
+      </c>
+      <c r="E126" s="8" t="inlineStr">
+        <is>
+          <t>Weekday / Minchah / Amida / Keduasha</t>
+        </is>
+      </c>
+      <c r="F126" s="19" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="25" customHeight="1">
+      <c r="A127" s="12" t="inlineStr">
+        <is>
+          <t>Mincha</t>
+        </is>
+      </c>
+      <c r="B127" s="12" t="inlineStr">
+        <is>
+          <t>Kingdom of David</t>
+        </is>
+      </c>
+      <c r="C127" s="12" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-ashkenaz-weekday-minchah-amida-kingdom-of-david</t>
+        </is>
+      </c>
+      <c r="D127" s="12" t="n">
+        <v>248</v>
+      </c>
+      <c r="E127" s="12" t="inlineStr">
+        <is>
+          <t>Weekday / Minchah / Amida / Kingdom of David</t>
+        </is>
+      </c>
+      <c r="F127" s="18" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="25" customHeight="1">
+      <c r="A128" s="8" t="inlineStr">
+        <is>
+          <t>Mincha</t>
+        </is>
+      </c>
+      <c r="B128" s="8" t="inlineStr">
+        <is>
+          <t>Knowledge</t>
+        </is>
+      </c>
+      <c r="C128" s="8" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-ashkenaz-weekday-minchah-amida-knowledge</t>
+        </is>
+      </c>
+      <c r="D128" s="8" t="n">
+        <v>240</v>
+      </c>
+      <c r="E128" s="8" t="inlineStr">
+        <is>
+          <t>Weekday / Minchah / Amida / Knowledge</t>
+        </is>
+      </c>
+      <c r="F128" s="19" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="25" customHeight="1">
+      <c r="A129" s="12" t="inlineStr">
+        <is>
+          <t>Mincha</t>
+        </is>
+      </c>
+      <c r="B129" s="12" t="inlineStr">
+        <is>
+          <t>Rebuilding Jerusalem</t>
+        </is>
+      </c>
+      <c r="C129" s="12" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-ashkenaz-weekday-minchah-amida-rebuilding-jerusalem</t>
+        </is>
+      </c>
+      <c r="D129" s="12" t="n">
+        <v>247</v>
+      </c>
+      <c r="E129" s="12" t="inlineStr">
+        <is>
+          <t>Weekday / Minchah / Amida / Rebuilding Jerusalem</t>
+        </is>
+      </c>
+      <c r="F129" s="18" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="25" customHeight="1">
+      <c r="A130" s="8" t="inlineStr">
+        <is>
+          <t>Mincha</t>
+        </is>
+      </c>
+      <c r="B130" s="8" t="inlineStr">
+        <is>
+          <t>Repentance</t>
+        </is>
+      </c>
+      <c r="C130" s="8" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-ashkenaz-weekday-minchah-amida-repentance</t>
+        </is>
+      </c>
+      <c r="D130" s="8" t="n">
+        <v>241</v>
+      </c>
+      <c r="E130" s="8" t="inlineStr">
+        <is>
+          <t>Weekday / Minchah / Amida / Repentance</t>
+        </is>
+      </c>
+      <c r="F130" s="19" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="25" customHeight="1">
+      <c r="A131" s="12" t="inlineStr">
+        <is>
+          <t>Mincha</t>
+        </is>
+      </c>
+      <c r="B131" s="12" t="inlineStr">
+        <is>
+          <t>Response to Prayer</t>
+        </is>
+      </c>
+      <c r="C131" s="12" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-ashkenaz-weekday-minchah-amida-response-to-prayer</t>
+        </is>
+      </c>
+      <c r="D131" s="12" t="n">
+        <v>249</v>
+      </c>
+      <c r="E131" s="12" t="inlineStr">
+        <is>
+          <t>Weekday / Minchah / Amida / Response to Prayer</t>
+        </is>
+      </c>
+      <c r="F131" s="18" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="25" customHeight="1">
+      <c r="A132" s="8" t="inlineStr">
+        <is>
+          <t>Mincha</t>
+        </is>
+      </c>
+      <c r="B132" s="8" t="inlineStr">
+        <is>
+          <t>Temple Service</t>
+        </is>
+      </c>
+      <c r="C132" s="8" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-ashkenaz-weekday-minchah-amida-temple-service</t>
+        </is>
+      </c>
+      <c r="D132" s="8" t="n">
+        <v>250</v>
+      </c>
+      <c r="E132" s="8" t="inlineStr">
+        <is>
+          <t>Weekday / Minchah / Amida / Temple Service</t>
+        </is>
+      </c>
+      <c r="F132" s="19" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="25" customHeight="1">
+      <c r="A133" s="12" t="inlineStr">
+        <is>
+          <t>Mincha</t>
+        </is>
+      </c>
+      <c r="B133" s="12" t="inlineStr">
+        <is>
+          <t>The Righteous</t>
+        </is>
+      </c>
+      <c r="C133" s="12" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-ashkenaz-weekday-minchah-amida-the-righteous</t>
+        </is>
+      </c>
+      <c r="D133" s="12" t="n">
+        <v>246</v>
+      </c>
+      <c r="E133" s="12" t="inlineStr">
+        <is>
+          <t>Weekday / Minchah / Amida / The Righteous</t>
+        </is>
+      </c>
+      <c r="F133" s="18" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="134" ht="25" customHeight="1">
+      <c r="A134" s="8" t="inlineStr">
+        <is>
+          <t>Mincha</t>
+        </is>
+      </c>
+      <c r="B134" s="8" t="inlineStr">
+        <is>
+          <t>Ashrei</t>
+        </is>
+      </c>
+      <c r="C134" s="8" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-ashkenaz-weekday-minchah-ashrei</t>
+        </is>
+      </c>
+      <c r="D134" s="8" t="n">
+        <v>238</v>
+      </c>
+      <c r="E134" s="8" t="inlineStr">
+        <is>
+          <t>Weekday / Minchah / Ashrei</t>
+        </is>
+      </c>
+      <c r="F134" s="19" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" ht="25" customHeight="1">
+      <c r="A135" s="12" t="inlineStr">
+        <is>
+          <t>Mincha</t>
+        </is>
+      </c>
+      <c r="B135" s="12" t="inlineStr">
+        <is>
+          <t>Alenu</t>
+        </is>
+      </c>
+      <c r="C135" s="12" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-ashkenaz-weekday-minchah-concluding-prayers-alenu</t>
+        </is>
+      </c>
+      <c r="D135" s="12" t="n">
+        <v>256</v>
+      </c>
+      <c r="E135" s="12" t="inlineStr">
+        <is>
+          <t>Weekday / Minchah / Concluding Prayers / Alenu</t>
+        </is>
+      </c>
+      <c r="F135" s="18" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" ht="25" customHeight="1">
+      <c r="A136" s="8" t="inlineStr">
+        <is>
+          <t>Mincha</t>
+        </is>
+      </c>
+      <c r="B136" s="8" t="inlineStr">
+        <is>
+          <t>Mourner's Kaddish</t>
+        </is>
+      </c>
+      <c r="C136" s="8" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-ashkenaz-weekday-minchah-concluding-prayers-mourner-s-kaddish</t>
+        </is>
+      </c>
+      <c r="D136" s="8" t="n">
+        <v>257</v>
+      </c>
+      <c r="E136" s="8" t="inlineStr">
+        <is>
+          <t>Weekday / Minchah / Concluding Prayers / Mourner's Kaddish</t>
+        </is>
+      </c>
+      <c r="F136" s="19" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" ht="25" customHeight="1">
+      <c r="A137" s="12" t="inlineStr">
+        <is>
+          <t>Mincha</t>
+        </is>
+      </c>
+      <c r="B137" s="12" t="inlineStr">
+        <is>
+          <t>Kaddish Shalem</t>
+        </is>
+      </c>
+      <c r="C137" s="12" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-ashkenaz-weekday-minchah-post-amidah-kaddish-shalem</t>
+        </is>
+      </c>
+      <c r="D137" s="12" t="n">
+        <v>255</v>
+      </c>
+      <c r="E137" s="12" t="inlineStr">
+        <is>
+          <t>Weekday / Minchah / Post Amidah / Kaddish Shalem</t>
+        </is>
+      </c>
+      <c r="F137" s="18" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" ht="25" customHeight="1">
+      <c r="A138" s="8" t="inlineStr">
+        <is>
+          <t>Mincha</t>
+        </is>
+      </c>
+      <c r="B138" s="8" t="inlineStr">
+        <is>
+          <t>Nefilat Appayim</t>
+        </is>
+      </c>
+      <c r="C138" s="8" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-ashkenaz-weekday-minchah-post-amidah-tachanun-nefilat-appayim</t>
+        </is>
+      </c>
+      <c r="D138" s="8" t="n">
+        <v>253</v>
+      </c>
+      <c r="E138" s="8" t="inlineStr">
+        <is>
+          <t>Weekday / Minchah / Post Amidah / Tachanun / Nefilat Appayim</t>
+        </is>
+      </c>
+      <c r="F138" s="19" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="139" ht="25" customHeight="1">
+      <c r="A139" s="12" t="inlineStr">
+        <is>
+          <t>Mincha</t>
+        </is>
+      </c>
+      <c r="B139" s="12" t="inlineStr">
+        <is>
+          <t>Shomer Yisrael</t>
+        </is>
+      </c>
+      <c r="C139" s="12" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-ashkenaz-weekday-minchah-post-amidah-tachanun-shomer-yisrael</t>
+        </is>
+      </c>
+      <c r="D139" s="12" t="n">
+        <v>254</v>
+      </c>
+      <c r="E139" s="12" t="inlineStr">
+        <is>
+          <t>Weekday / Minchah / Post Amidah / Tachanun / Shomer Yisrael</t>
+        </is>
+      </c>
+      <c r="F139" s="18" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="140" ht="25" customHeight="1">
+      <c r="A140" s="8" t="inlineStr">
+        <is>
+          <t>Mincha</t>
+        </is>
+      </c>
+      <c r="B140" s="8" t="inlineStr">
+        <is>
+          <t>Avinu Malkeinu</t>
+        </is>
+      </c>
+      <c r="C140" s="8" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-sefard-weekday-mincha-avinu-malkeinu</t>
+        </is>
+      </c>
+      <c r="D140" s="8" t="n">
+        <v>349</v>
+      </c>
+      <c r="E140" s="8" t="inlineStr">
+        <is>
+          <t>Weekday Mincha / Avinu Malkeinu</t>
+        </is>
+      </c>
+      <c r="F140" s="19" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="141" ht="25" customHeight="1">
+      <c r="A141" s="12" t="inlineStr">
+        <is>
+          <t>Mincha</t>
+        </is>
+      </c>
+      <c r="B141" s="12" t="inlineStr">
+        <is>
+          <t>Korbanot</t>
+        </is>
+      </c>
+      <c r="C141" s="12" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-sefard-weekday-mincha-korbanot</t>
+        </is>
+      </c>
+      <c r="D141" s="12" t="n">
+        <v>347</v>
+      </c>
+      <c r="E141" s="12" t="inlineStr">
+        <is>
+          <t>Weekday Mincha / Korbanot</t>
+        </is>
+      </c>
+      <c r="F141" s="18" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="142" ht="25" customHeight="1">
+      <c r="A142" s="8" t="inlineStr">
+        <is>
+          <t>Mincha</t>
+        </is>
+      </c>
+      <c r="B142" s="8" t="inlineStr">
+        <is>
+          <t>Tachanun</t>
+        </is>
+      </c>
+      <c r="C142" s="8" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-sefard-weekday-mincha-tachanun</t>
+        </is>
+      </c>
+      <c r="D142" s="8" t="n">
+        <v>348</v>
+      </c>
+      <c r="E142" s="8" t="inlineStr">
+        <is>
+          <t>Weekday Mincha / Tachanun</t>
+        </is>
+      </c>
+      <c r="F142" s="19" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="25" customHeight="1">
+      <c r="A143" s="12" t="inlineStr">
         <is>
           <t>Maariv</t>
         </is>
       </c>
-      <c r="C7" s="17" t="inlineStr">
-        <is>
-          <t>Ashkenaz</t>
-        </is>
-      </c>
-      <c r="D7" s="17" t="inlineStr">
-        <is>
-          <t>No Hebrew candidate is ready for approval.</t>
-        </is>
-      </c>
-      <c r="E7" s="17" t="inlineStr">
-        <is>
-          <t>Siddur Ashkenaz, Weekday Maariv. Service collection, not a single prayer. Source snapshot not yet pinned; section-level source plan required.</t>
-        </is>
-      </c>
-      <c r="F7" s="17" t="inlineStr"/>
+      <c r="B143" s="12" t="inlineStr">
+        <is>
+          <t>Mourner's Kaddish</t>
+        </is>
+      </c>
+      <c r="C143" s="12" t="inlineStr">
+        <is>
+          <t>sefaria-machzor-rosh-hashanah-ashkenaz-maariv-mourner-s-kaddish</t>
+        </is>
+      </c>
+      <c r="D143" s="12" t="n">
+        <v>418</v>
+      </c>
+      <c r="E143" s="12" t="inlineStr">
+        <is>
+          <t>Maariv / Mourner's Kaddish</t>
+        </is>
+      </c>
+      <c r="F143" s="18" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="25" customHeight="1">
+      <c r="A144" s="8" t="inlineStr">
+        <is>
+          <t>Maariv</t>
+        </is>
+      </c>
+      <c r="B144" s="8" t="inlineStr">
+        <is>
+          <t>Mourner's Kaddish</t>
+        </is>
+      </c>
+      <c r="C144" s="8" t="inlineStr">
+        <is>
+          <t>sefaria-machzor-rosh-hashanah-ashkenaz-linear-maariv-mourner-s-kaddish</t>
+        </is>
+      </c>
+      <c r="D144" s="8" t="n">
+        <v>433</v>
+      </c>
+      <c r="E144" s="8" t="inlineStr">
+        <is>
+          <t>Maariv / Mourner's Kaddish</t>
+        </is>
+      </c>
+      <c r="F144" s="19" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="145" ht="25" customHeight="1">
+      <c r="A145" s="12" t="inlineStr">
+        <is>
+          <t>Maariv</t>
+        </is>
+      </c>
+      <c r="B145" s="12" t="inlineStr">
+        <is>
+          <t>Aleinu</t>
+        </is>
+      </c>
+      <c r="C145" s="12" t="inlineStr">
+        <is>
+          <t>sefaria-shabbat-siddur-sefard-linear-maariv-service-for-shabbos-and-yom-tov-aleinu</t>
+        </is>
+      </c>
+      <c r="D145" s="12" t="n">
+        <v>376</v>
+      </c>
+      <c r="E145" s="12" t="inlineStr">
+        <is>
+          <t>Maariv Service for Shabbos and Yom Tov / Aleinu</t>
+        </is>
+      </c>
+      <c r="F145" s="18" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="146" ht="25" customHeight="1">
+      <c r="A146" s="8" t="inlineStr">
+        <is>
+          <t>Maariv</t>
+        </is>
+      </c>
+      <c r="B146" s="8" t="inlineStr">
+        <is>
+          <t>Aleinu</t>
+        </is>
+      </c>
+      <c r="C146" s="8" t="inlineStr">
+        <is>
+          <t>sefaria-shabbat-siddur-sefard-linear-maariv-service-for-the-conclusion-of-shabbos-aleinu</t>
+        </is>
+      </c>
+      <c r="D146" s="8" t="n">
+        <v>389</v>
+      </c>
+      <c r="E146" s="8" t="inlineStr">
+        <is>
+          <t>Maariv Service for the Conclusion of Shabbos / Aleinu</t>
+        </is>
+      </c>
+      <c r="F146" s="19" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="147" ht="25" customHeight="1">
+      <c r="A147" s="12" t="inlineStr">
+        <is>
+          <t>Maariv</t>
+        </is>
+      </c>
+      <c r="B147" s="12" t="inlineStr">
+        <is>
+          <t>Mourner's Kaddish</t>
+        </is>
+      </c>
+      <c r="C147" s="12" t="inlineStr">
+        <is>
+          <t>sefaria-machzor-yom-kippur-ashkenaz-linear-maariv-service-for-yom-kippur-eve-mourner-s-kaddish</t>
+        </is>
+      </c>
+      <c r="D147" s="12" t="n">
+        <v>440</v>
+      </c>
+      <c r="E147" s="12" t="inlineStr">
+        <is>
+          <t>Maariv Service for Yom Kippur Eve / Mourner's Kaddish</t>
+        </is>
+      </c>
+      <c r="F147" s="18" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="148" ht="25" customHeight="1">
+      <c r="A148" s="8" t="inlineStr">
+        <is>
+          <t>Maariv</t>
+        </is>
+      </c>
+      <c r="B148" s="8" t="inlineStr">
+        <is>
+          <t>Adon Olam</t>
+        </is>
+      </c>
+      <c r="C148" s="8" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-ashkenaz-shabbat-maariv-adon-olam</t>
+        </is>
+      </c>
+      <c r="D148" s="8" t="n">
+        <v>313</v>
+      </c>
+      <c r="E148" s="8" t="inlineStr">
+        <is>
+          <t>Shabbat / Maariv / Adon Olam</t>
+        </is>
+      </c>
+      <c r="F148" s="19" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="149" ht="25" customHeight="1">
+      <c r="A149" s="12" t="inlineStr">
+        <is>
+          <t>Maariv</t>
+        </is>
+      </c>
+      <c r="B149" s="12" t="inlineStr">
+        <is>
+          <t>Aleinu</t>
+        </is>
+      </c>
+      <c r="C149" s="12" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-ashkenaz-shabbat-maariv-aleinu</t>
+        </is>
+      </c>
+      <c r="D149" s="12" t="n">
+        <v>309</v>
+      </c>
+      <c r="E149" s="12" t="inlineStr">
+        <is>
+          <t>Shabbat / Maariv / Aleinu</t>
+        </is>
+      </c>
+      <c r="F149" s="18" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="150" ht="25" customHeight="1">
+      <c r="A150" s="8" t="inlineStr">
+        <is>
+          <t>Maariv</t>
+        </is>
+      </c>
+      <c r="B150" s="8" t="inlineStr">
+        <is>
+          <t>Concluding Passage</t>
+        </is>
+      </c>
+      <c r="C150" s="8" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-ashkenaz-shabbat-maariv-amidah-concluding-passage</t>
+        </is>
+      </c>
+      <c r="D150" s="8" t="n">
+        <v>305</v>
+      </c>
+      <c r="E150" s="8" t="inlineStr">
+        <is>
+          <t>Shabbat / Maariv / Amidah / Concluding Passage</t>
+        </is>
+      </c>
+      <c r="F150" s="19" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="151" ht="25" customHeight="1">
+      <c r="A151" s="12" t="inlineStr">
+        <is>
+          <t>Maariv</t>
+        </is>
+      </c>
+      <c r="B151" s="12" t="inlineStr">
+        <is>
+          <t>Holines of God's Name</t>
+        </is>
+      </c>
+      <c r="C151" s="12" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-ashkenaz-shabbat-maariv-amidah-holines-of-god-s-name</t>
+        </is>
+      </c>
+      <c r="D151" s="12" t="n">
+        <v>301</v>
+      </c>
+      <c r="E151" s="12" t="inlineStr">
+        <is>
+          <t>Shabbat / Maariv / Amidah / Holines of God's Name</t>
+        </is>
+      </c>
+      <c r="F151" s="18" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="152" ht="25" customHeight="1">
+      <c r="A152" s="8" t="inlineStr">
+        <is>
+          <t>Maariv</t>
+        </is>
+      </c>
+      <c r="B152" s="8" t="inlineStr">
+        <is>
+          <t>Peace</t>
+        </is>
+      </c>
+      <c r="C152" s="8" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-ashkenaz-shabbat-maariv-amidah-peace</t>
+        </is>
+      </c>
+      <c r="D152" s="8" t="n">
+        <v>304</v>
+      </c>
+      <c r="E152" s="8" t="inlineStr">
+        <is>
+          <t>Shabbat / Maariv / Amidah / Peace</t>
+        </is>
+      </c>
+      <c r="F152" s="19" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="153" ht="25" customHeight="1">
+      <c r="A153" s="12" t="inlineStr">
+        <is>
+          <t>Maariv</t>
+        </is>
+      </c>
+      <c r="B153" s="12" t="inlineStr">
+        <is>
+          <t>Sanctity of the Day</t>
+        </is>
+      </c>
+      <c r="C153" s="12" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-ashkenaz-shabbat-maariv-amidah-sanctity-of-the-day</t>
+        </is>
+      </c>
+      <c r="D153" s="12" t="n">
+        <v>302</v>
+      </c>
+      <c r="E153" s="12" t="inlineStr">
+        <is>
+          <t>Shabbat / Maariv / Amidah / Sanctity of the Day</t>
+        </is>
+      </c>
+      <c r="F153" s="18" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="154" ht="25" customHeight="1">
+      <c r="A154" s="8" t="inlineStr">
+        <is>
+          <t>Maariv</t>
+        </is>
+      </c>
+      <c r="B154" s="8" t="inlineStr">
+        <is>
+          <t>Temple Service</t>
+        </is>
+      </c>
+      <c r="C154" s="8" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-ashkenaz-shabbat-maariv-amidah-temple-service</t>
+        </is>
+      </c>
+      <c r="D154" s="8" t="n">
+        <v>303</v>
+      </c>
+      <c r="E154" s="8" t="inlineStr">
+        <is>
+          <t>Shabbat / Maariv / Amidah / Temple Service</t>
+        </is>
+      </c>
+      <c r="F154" s="19" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="155" ht="25" customHeight="1">
+      <c r="A155" s="12" t="inlineStr">
+        <is>
+          <t>Maariv</t>
+        </is>
+      </c>
+      <c r="B155" s="12" t="inlineStr">
+        <is>
+          <t>First Blessing after Shema</t>
+        </is>
+      </c>
+      <c r="C155" s="12" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-ashkenaz-shabbat-maariv-blessings-of-the-shema-first-blessing-after-shema</t>
+        </is>
+      </c>
+      <c r="D155" s="12" t="n">
+        <v>298</v>
+      </c>
+      <c r="E155" s="12" t="inlineStr">
+        <is>
+          <t>Shabbat / Maariv / Blessings of the Shema / First Blessing after Shema</t>
+        </is>
+      </c>
+      <c r="F155" s="18" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="156" ht="25" customHeight="1">
+      <c r="A156" s="8" t="inlineStr">
+        <is>
+          <t>Maariv</t>
+        </is>
+      </c>
+      <c r="B156" s="8" t="inlineStr">
+        <is>
+          <t>First Blessing before Shema</t>
+        </is>
+      </c>
+      <c r="C156" s="8" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-ashkenaz-shabbat-maariv-blessings-of-the-shema-first-blessing-before-shema</t>
+        </is>
+      </c>
+      <c r="D156" s="8" t="n">
+        <v>296</v>
+      </c>
+      <c r="E156" s="8" t="inlineStr">
+        <is>
+          <t>Shabbat / Maariv / Blessings of the Shema / First Blessing before Shema</t>
+        </is>
+      </c>
+      <c r="F156" s="19" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="157" ht="25" customHeight="1">
+      <c r="A157" s="12" t="inlineStr">
+        <is>
+          <t>Maariv</t>
+        </is>
+      </c>
+      <c r="B157" s="12" t="inlineStr">
+        <is>
+          <t>Second Blessing after Shema</t>
+        </is>
+      </c>
+      <c r="C157" s="12" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-ashkenaz-shabbat-maariv-blessings-of-the-shema-second-blessing-after-shema</t>
+        </is>
+      </c>
+      <c r="D157" s="12" t="n">
+        <v>299</v>
+      </c>
+      <c r="E157" s="12" t="inlineStr">
+        <is>
+          <t>Shabbat / Maariv / Blessings of the Shema / Second Blessing after Shema</t>
+        </is>
+      </c>
+      <c r="F157" s="18" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="158" ht="25" customHeight="1">
+      <c r="A158" s="8" t="inlineStr">
+        <is>
+          <t>Maariv</t>
+        </is>
+      </c>
+      <c r="B158" s="8" t="inlineStr">
+        <is>
+          <t>Second Blessing before Shema</t>
+        </is>
+      </c>
+      <c r="C158" s="8" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-ashkenaz-shabbat-maariv-blessings-of-the-shema-second-blessing-before-shema</t>
+        </is>
+      </c>
+      <c r="D158" s="8" t="n">
+        <v>297</v>
+      </c>
+      <c r="E158" s="8" t="inlineStr">
+        <is>
+          <t>Shabbat / Maariv / Blessings of the Shema / Second Blessing before Shema</t>
+        </is>
+      </c>
+      <c r="F158" s="19" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="159" ht="25" customHeight="1">
+      <c r="A159" s="12" t="inlineStr">
+        <is>
+          <t>Maariv</t>
+        </is>
+      </c>
+      <c r="B159" s="12" t="inlineStr">
+        <is>
+          <t>Half Kaddish</t>
+        </is>
+      </c>
+      <c r="C159" s="12" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-ashkenaz-shabbat-maariv-half-kaddish</t>
+        </is>
+      </c>
+      <c r="D159" s="12" t="n">
+        <v>300</v>
+      </c>
+      <c r="E159" s="12" t="inlineStr">
+        <is>
+          <t>Shabbat / Maariv / Half Kaddish</t>
+        </is>
+      </c>
+      <c r="F159" s="18" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="160" ht="25" customHeight="1">
+      <c r="A160" s="8" t="inlineStr">
+        <is>
+          <t>Maariv</t>
+        </is>
+      </c>
+      <c r="B160" s="8" t="inlineStr">
+        <is>
+          <t>Kaddish Shalem</t>
+        </is>
+      </c>
+      <c r="C160" s="8" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-ashkenaz-shabbat-maariv-kaddish-shalem</t>
+        </is>
+      </c>
+      <c r="D160" s="8" t="n">
+        <v>308</v>
+      </c>
+      <c r="E160" s="8" t="inlineStr">
+        <is>
+          <t>Shabbat / Maariv / Kaddish Shalem</t>
+        </is>
+      </c>
+      <c r="F160" s="19" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="161" ht="25" customHeight="1">
+      <c r="A161" s="12" t="inlineStr">
+        <is>
+          <t>Maariv</t>
+        </is>
+      </c>
+      <c r="B161" s="12" t="inlineStr">
+        <is>
+          <t>LeDavid</t>
+        </is>
+      </c>
+      <c r="C161" s="12" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-ashkenaz-shabbat-maariv-ledavid</t>
+        </is>
+      </c>
+      <c r="D161" s="12" t="n">
+        <v>311</v>
+      </c>
+      <c r="E161" s="12" t="inlineStr">
+        <is>
+          <t>Shabbat / Maariv / LeDavid</t>
+        </is>
+      </c>
+      <c r="F161" s="18" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="162" ht="25" customHeight="1">
+      <c r="A162" s="8" t="inlineStr">
+        <is>
+          <t>Maariv</t>
+        </is>
+      </c>
+      <c r="B162" s="8" t="inlineStr">
+        <is>
+          <t>Me'ein Sheva</t>
+        </is>
+      </c>
+      <c r="C162" s="8" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-ashkenaz-shabbat-maariv-me-ein-sheva</t>
+        </is>
+      </c>
+      <c r="D162" s="8" t="n">
+        <v>307</v>
+      </c>
+      <c r="E162" s="8" t="inlineStr">
+        <is>
+          <t>Shabbat / Maariv / Me'ein Sheva</t>
+        </is>
+      </c>
+      <c r="F162" s="19" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="163" ht="25" customHeight="1">
+      <c r="A163" s="12" t="inlineStr">
+        <is>
+          <t>Maariv</t>
+        </is>
+      </c>
+      <c r="B163" s="12" t="inlineStr">
+        <is>
+          <t>Mourner's Kaddish</t>
+        </is>
+      </c>
+      <c r="C163" s="12" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-ashkenaz-shabbat-maariv-mourner-s-kaddish</t>
+        </is>
+      </c>
+      <c r="D163" s="12" t="n">
+        <v>310</v>
+      </c>
+      <c r="E163" s="12" t="inlineStr">
+        <is>
+          <t>Shabbat / Maariv / Mourner's Kaddish</t>
+        </is>
+      </c>
+      <c r="F163" s="18" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="164" ht="25" customHeight="1">
+      <c r="A164" s="8" t="inlineStr">
+        <is>
+          <t>Maariv</t>
+        </is>
+      </c>
+      <c r="B164" s="8" t="inlineStr">
+        <is>
+          <t>Vay'chulu</t>
+        </is>
+      </c>
+      <c r="C164" s="8" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-ashkenaz-shabbat-maariv-vay-chulu</t>
+        </is>
+      </c>
+      <c r="D164" s="8" t="n">
+        <v>306</v>
+      </c>
+      <c r="E164" s="8" t="inlineStr">
+        <is>
+          <t>Shabbat / Maariv / Vay'chulu</t>
+        </is>
+      </c>
+      <c r="F164" s="19" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="165" ht="25" customHeight="1">
+      <c r="A165" s="12" t="inlineStr">
+        <is>
+          <t>Maariv</t>
+        </is>
+      </c>
+      <c r="B165" s="12" t="inlineStr">
+        <is>
+          <t>Yigdal</t>
+        </is>
+      </c>
+      <c r="C165" s="12" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-ashkenaz-shabbat-maariv-yigdal</t>
+        </is>
+      </c>
+      <c r="D165" s="12" t="n">
+        <v>312</v>
+      </c>
+      <c r="E165" s="12" t="inlineStr">
+        <is>
+          <t>Shabbat / Maariv / Yigdal</t>
+        </is>
+      </c>
+      <c r="F165" s="18" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="166" ht="25" customHeight="1">
+      <c r="A166" s="8" t="inlineStr">
+        <is>
+          <t>Maariv</t>
+        </is>
+      </c>
+      <c r="B166" s="8" t="inlineStr">
+        <is>
+          <t>Viyehi Noam</t>
+        </is>
+      </c>
+      <c r="C166" s="8" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-ashkenaz-weekday-maariv-additions-for-motza-ei-shabbat-viyehi-noam</t>
+        </is>
+      </c>
+      <c r="D166" s="8" t="n">
+        <v>279</v>
+      </c>
+      <c r="E166" s="8" t="inlineStr">
+        <is>
+          <t>Weekday / Maariv / Additions for Motza'ei Shabbat / Viyehi Noam</t>
+        </is>
+      </c>
+      <c r="F166" s="19" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="167" ht="25" customHeight="1">
+      <c r="A167" s="12" t="inlineStr">
+        <is>
+          <t>Maariv</t>
+        </is>
+      </c>
+      <c r="B167" s="12" t="inlineStr">
+        <is>
+          <t>Alenu</t>
+        </is>
+      </c>
+      <c r="C167" s="12" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-ashkenaz-weekday-maariv-alenu</t>
+        </is>
+      </c>
+      <c r="D167" s="12" t="n">
+        <v>280</v>
+      </c>
+      <c r="E167" s="12" t="inlineStr">
+        <is>
+          <t>Weekday / Maariv / Alenu</t>
+        </is>
+      </c>
+      <c r="F167" s="18" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="168" ht="25" customHeight="1">
+      <c r="A168" s="8" t="inlineStr">
+        <is>
+          <t>Maariv</t>
+        </is>
+      </c>
+      <c r="B168" s="8" t="inlineStr">
+        <is>
+          <t>Against Enemies</t>
+        </is>
+      </c>
+      <c r="C168" s="8" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-ashkenaz-weekday-maariv-amidah-against-enemies</t>
+        </is>
+      </c>
+      <c r="D168" s="8" t="n">
+        <v>272</v>
+      </c>
+      <c r="E168" s="8" t="inlineStr">
+        <is>
+          <t>Weekday / Maariv / Amidah / Against Enemies</t>
+        </is>
+      </c>
+      <c r="F168" s="19" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="169" ht="25" customHeight="1">
+      <c r="A169" s="12" t="inlineStr">
+        <is>
+          <t>Maariv</t>
+        </is>
+      </c>
+      <c r="B169" s="12" t="inlineStr">
+        <is>
+          <t>Concluding Passage</t>
+        </is>
+      </c>
+      <c r="C169" s="12" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-ashkenaz-weekday-maariv-amidah-concluding-passage</t>
+        </is>
+      </c>
+      <c r="D169" s="12" t="n">
+        <v>278</v>
+      </c>
+      <c r="E169" s="12" t="inlineStr">
+        <is>
+          <t>Weekday / Maariv / Amidah / Concluding Passage</t>
+        </is>
+      </c>
+      <c r="F169" s="18" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="170" ht="25" customHeight="1">
+      <c r="A170" s="8" t="inlineStr">
+        <is>
+          <t>Maariv</t>
+        </is>
+      </c>
+      <c r="B170" s="8" t="inlineStr">
+        <is>
+          <t>Forgiveness</t>
+        </is>
+      </c>
+      <c r="C170" s="8" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-ashkenaz-weekday-maariv-amidah-forgiveness</t>
+        </is>
+      </c>
+      <c r="D170" s="8" t="n">
+        <v>268</v>
+      </c>
+      <c r="E170" s="8" t="inlineStr">
+        <is>
+          <t>Weekday / Maariv / Amidah / Forgiveness</t>
+        </is>
+      </c>
+      <c r="F170" s="19" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="171" ht="25" customHeight="1">
+      <c r="A171" s="12" t="inlineStr">
+        <is>
+          <t>Maariv</t>
+        </is>
+      </c>
+      <c r="B171" s="12" t="inlineStr">
+        <is>
+          <t>Gathering the Exiles</t>
+        </is>
+      </c>
+      <c r="C171" s="12" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-ashkenaz-weekday-maariv-amidah-gathering-the-exiles</t>
+        </is>
+      </c>
+      <c r="D171" s="12" t="n">
+        <v>271</v>
+      </c>
+      <c r="E171" s="12" t="inlineStr">
+        <is>
+          <t>Weekday / Maariv / Amidah / Gathering the Exiles</t>
+        </is>
+      </c>
+      <c r="F171" s="18" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="172" ht="25" customHeight="1">
+      <c r="A172" s="8" t="inlineStr">
+        <is>
+          <t>Maariv</t>
+        </is>
+      </c>
+      <c r="B172" s="8" t="inlineStr">
+        <is>
+          <t>Healing</t>
+        </is>
+      </c>
+      <c r="C172" s="8" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-ashkenaz-weekday-maariv-amidah-healing</t>
+        </is>
+      </c>
+      <c r="D172" s="8" t="n">
+        <v>270</v>
+      </c>
+      <c r="E172" s="8" t="inlineStr">
+        <is>
+          <t>Weekday / Maariv / Amidah / Healing</t>
+        </is>
+      </c>
+      <c r="F172" s="19" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="173" ht="25" customHeight="1">
+      <c r="A173" s="12" t="inlineStr">
+        <is>
+          <t>Maariv</t>
+        </is>
+      </c>
+      <c r="B173" s="12" t="inlineStr">
+        <is>
+          <t>Kingdom of David</t>
+        </is>
+      </c>
+      <c r="C173" s="12" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-ashkenaz-weekday-maariv-amidah-kingdom-of-david</t>
+        </is>
+      </c>
+      <c r="D173" s="12" t="n">
+        <v>275</v>
+      </c>
+      <c r="E173" s="12" t="inlineStr">
+        <is>
+          <t>Weekday / Maariv / Amidah / Kingdom of David</t>
+        </is>
+      </c>
+      <c r="F173" s="18" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="174" ht="25" customHeight="1">
+      <c r="A174" s="8" t="inlineStr">
+        <is>
+          <t>Maariv</t>
+        </is>
+      </c>
+      <c r="B174" s="8" t="inlineStr">
+        <is>
+          <t>Knowledge</t>
+        </is>
+      </c>
+      <c r="C174" s="8" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-ashkenaz-weekday-maariv-amidah-knowledge</t>
+        </is>
+      </c>
+      <c r="D174" s="8" t="n">
+        <v>266</v>
+      </c>
+      <c r="E174" s="8" t="inlineStr">
+        <is>
+          <t>Weekday / Maariv / Amidah / Knowledge</t>
+        </is>
+      </c>
+      <c r="F174" s="19" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="175" ht="25" customHeight="1">
+      <c r="A175" s="12" t="inlineStr">
+        <is>
+          <t>Maariv</t>
+        </is>
+      </c>
+      <c r="B175" s="12" t="inlineStr">
+        <is>
+          <t>Rebuilding Jerusalem</t>
+        </is>
+      </c>
+      <c r="C175" s="12" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-ashkenaz-weekday-maariv-amidah-rebuilding-jerusalem</t>
+        </is>
+      </c>
+      <c r="D175" s="12" t="n">
+        <v>274</v>
+      </c>
+      <c r="E175" s="12" t="inlineStr">
+        <is>
+          <t>Weekday / Maariv / Amidah / Rebuilding Jerusalem</t>
+        </is>
+      </c>
+      <c r="F175" s="18" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="176" ht="25" customHeight="1">
+      <c r="A176" s="8" t="inlineStr">
+        <is>
+          <t>Maariv</t>
+        </is>
+      </c>
+      <c r="B176" s="8" t="inlineStr">
+        <is>
+          <t>Redemption</t>
+        </is>
+      </c>
+      <c r="C176" s="8" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-ashkenaz-weekday-maariv-amidah-redemption</t>
+        </is>
+      </c>
+      <c r="D176" s="8" t="n">
+        <v>269</v>
+      </c>
+      <c r="E176" s="8" t="inlineStr">
+        <is>
+          <t>Weekday / Maariv / Amidah / Redemption</t>
+        </is>
+      </c>
+      <c r="F176" s="19" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="177" ht="25" customHeight="1">
+      <c r="A177" s="12" t="inlineStr">
+        <is>
+          <t>Maariv</t>
+        </is>
+      </c>
+      <c r="B177" s="12" t="inlineStr">
+        <is>
+          <t>Repentance</t>
+        </is>
+      </c>
+      <c r="C177" s="12" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-ashkenaz-weekday-maariv-amidah-repentance</t>
+        </is>
+      </c>
+      <c r="D177" s="12" t="n">
+        <v>267</v>
+      </c>
+      <c r="E177" s="12" t="inlineStr">
+        <is>
+          <t>Weekday / Maariv / Amidah / Repentance</t>
+        </is>
+      </c>
+      <c r="F177" s="18" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="178" ht="25" customHeight="1">
+      <c r="A178" s="8" t="inlineStr">
+        <is>
+          <t>Maariv</t>
+        </is>
+      </c>
+      <c r="B178" s="8" t="inlineStr">
+        <is>
+          <t>Response to Prayer</t>
+        </is>
+      </c>
+      <c r="C178" s="8" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-ashkenaz-weekday-maariv-amidah-response-to-prayer</t>
+        </is>
+      </c>
+      <c r="D178" s="8" t="n">
+        <v>276</v>
+      </c>
+      <c r="E178" s="8" t="inlineStr">
+        <is>
+          <t>Weekday / Maariv / Amidah / Response to Prayer</t>
+        </is>
+      </c>
+      <c r="F178" s="19" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="179" ht="25" customHeight="1">
+      <c r="A179" s="12" t="inlineStr">
+        <is>
+          <t>Maariv</t>
+        </is>
+      </c>
+      <c r="B179" s="12" t="inlineStr">
+        <is>
+          <t>Temple Service</t>
+        </is>
+      </c>
+      <c r="C179" s="12" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-ashkenaz-weekday-maariv-amidah-temple-service</t>
+        </is>
+      </c>
+      <c r="D179" s="12" t="n">
+        <v>277</v>
+      </c>
+      <c r="E179" s="12" t="inlineStr">
+        <is>
+          <t>Weekday / Maariv / Amidah / Temple Service</t>
+        </is>
+      </c>
+      <c r="F179" s="18" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="180" ht="25" customHeight="1">
+      <c r="A180" s="8" t="inlineStr">
+        <is>
+          <t>Maariv</t>
+        </is>
+      </c>
+      <c r="B180" s="8" t="inlineStr">
+        <is>
+          <t>The Righteous</t>
+        </is>
+      </c>
+      <c r="C180" s="8" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-ashkenaz-weekday-maariv-amidah-the-righteous</t>
+        </is>
+      </c>
+      <c r="D180" s="8" t="n">
+        <v>273</v>
+      </c>
+      <c r="E180" s="8" t="inlineStr">
+        <is>
+          <t>Weekday / Maariv / Amidah / The Righteous</t>
+        </is>
+      </c>
+      <c r="F180" s="19" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="181" ht="25" customHeight="1">
+      <c r="A181" s="12" t="inlineStr">
+        <is>
+          <t>Maariv</t>
+        </is>
+      </c>
+      <c r="B181" s="12" t="inlineStr">
+        <is>
+          <t>Barchu</t>
+        </is>
+      </c>
+      <c r="C181" s="12" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-ashkenaz-weekday-maariv-barchu</t>
+        </is>
+      </c>
+      <c r="D181" s="12" t="n">
+        <v>259</v>
+      </c>
+      <c r="E181" s="12" t="inlineStr">
+        <is>
+          <t>Weekday / Maariv / Barchu</t>
+        </is>
+      </c>
+      <c r="F181" s="18" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="182" ht="25" customHeight="1">
+      <c r="A182" s="8" t="inlineStr">
+        <is>
+          <t>Maariv</t>
+        </is>
+      </c>
+      <c r="B182" s="8" t="inlineStr">
+        <is>
+          <t>First Blessing after Shema</t>
+        </is>
+      </c>
+      <c r="C182" s="8" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-ashkenaz-weekday-maariv-blessings-of-the-shema-first-blessing-after-shema</t>
+        </is>
+      </c>
+      <c r="D182" s="8" t="n">
+        <v>262</v>
+      </c>
+      <c r="E182" s="8" t="inlineStr">
+        <is>
+          <t>Weekday / Maariv / Blessings of the Shema / First Blessing after Shema</t>
+        </is>
+      </c>
+      <c r="F182" s="19" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="183" ht="25" customHeight="1">
+      <c r="A183" s="12" t="inlineStr">
+        <is>
+          <t>Maariv</t>
+        </is>
+      </c>
+      <c r="B183" s="12" t="inlineStr">
+        <is>
+          <t>First Blessing before Shema</t>
+        </is>
+      </c>
+      <c r="C183" s="12" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-ashkenaz-weekday-maariv-blessings-of-the-shema-first-blessing-before-shema</t>
+        </is>
+      </c>
+      <c r="D183" s="12" t="n">
+        <v>260</v>
+      </c>
+      <c r="E183" s="12" t="inlineStr">
+        <is>
+          <t>Weekday / Maariv / Blessings of the Shema / First Blessing before Shema</t>
+        </is>
+      </c>
+      <c r="F183" s="18" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="184" ht="25" customHeight="1">
+      <c r="A184" s="8" t="inlineStr">
+        <is>
+          <t>Maariv</t>
+        </is>
+      </c>
+      <c r="B184" s="8" t="inlineStr">
+        <is>
+          <t>Half Kaddish</t>
+        </is>
+      </c>
+      <c r="C184" s="8" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-ashkenaz-weekday-maariv-blessings-of-the-shema-half-kaddish</t>
+        </is>
+      </c>
+      <c r="D184" s="8" t="n">
+        <v>265</v>
+      </c>
+      <c r="E184" s="8" t="inlineStr">
+        <is>
+          <t>Weekday / Maariv / Blessings of the Shema / Half Kaddish</t>
+        </is>
+      </c>
+      <c r="F184" s="19" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="185" ht="25" customHeight="1">
+      <c r="A185" s="12" t="inlineStr">
+        <is>
+          <t>Maariv</t>
+        </is>
+      </c>
+      <c r="B185" s="12" t="inlineStr">
+        <is>
+          <t>Second Blessing after Shema</t>
+        </is>
+      </c>
+      <c r="C185" s="12" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-ashkenaz-weekday-maariv-blessings-of-the-shema-second-blessing-after-shema</t>
+        </is>
+      </c>
+      <c r="D185" s="12" t="n">
+        <v>263</v>
+      </c>
+      <c r="E185" s="12" t="inlineStr">
+        <is>
+          <t>Weekday / Maariv / Blessings of the Shema / Second Blessing after Shema</t>
+        </is>
+      </c>
+      <c r="F185" s="18" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="186" ht="25" customHeight="1">
+      <c r="A186" s="8" t="inlineStr">
+        <is>
+          <t>Maariv</t>
+        </is>
+      </c>
+      <c r="B186" s="8" t="inlineStr">
+        <is>
+          <t>Second Blessing before Shema</t>
+        </is>
+      </c>
+      <c r="C186" s="8" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-ashkenaz-weekday-maariv-blessings-of-the-shema-second-blessing-before-shema</t>
+        </is>
+      </c>
+      <c r="D186" s="8" t="n">
+        <v>261</v>
+      </c>
+      <c r="E186" s="8" t="inlineStr">
+        <is>
+          <t>Weekday / Maariv / Blessings of the Shema / Second Blessing before Shema</t>
+        </is>
+      </c>
+      <c r="F186" s="19" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="187" ht="25" customHeight="1">
+      <c r="A187" s="12" t="inlineStr">
+        <is>
+          <t>Maariv</t>
+        </is>
+      </c>
+      <c r="B187" s="12" t="inlineStr">
+        <is>
+          <t>Third Blessing after Shema</t>
+        </is>
+      </c>
+      <c r="C187" s="12" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-ashkenaz-weekday-maariv-blessings-of-the-shema-third-blessing-after-shema</t>
+        </is>
+      </c>
+      <c r="D187" s="12" t="n">
+        <v>264</v>
+      </c>
+      <c r="E187" s="12" t="inlineStr">
+        <is>
+          <t>Weekday / Maariv / Blessings of the Shema / Third Blessing after Shema</t>
+        </is>
+      </c>
+      <c r="F187" s="18" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="188" ht="25" customHeight="1">
+      <c r="A188" s="8" t="inlineStr">
+        <is>
+          <t>Maariv</t>
+        </is>
+      </c>
+      <c r="B188" s="8" t="inlineStr">
+        <is>
+          <t>Bedtime Shema</t>
+        </is>
+      </c>
+      <c r="C188" s="8" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-ashkenaz-weekday-maariv-keri-at-shema-al-hamita</t>
+        </is>
+      </c>
+      <c r="D188" s="8" t="n">
+        <v>283</v>
+      </c>
+      <c r="E188" s="8" t="inlineStr">
+        <is>
+          <t>Weekday / Maariv / Keri'at Shema al Hamita</t>
+        </is>
+      </c>
+      <c r="F188" s="19" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="189" ht="25" customHeight="1">
+      <c r="A189" s="12" t="inlineStr">
+        <is>
+          <t>Maariv</t>
+        </is>
+      </c>
+      <c r="B189" s="12" t="inlineStr">
+        <is>
+          <t>LeDavid</t>
+        </is>
+      </c>
+      <c r="C189" s="12" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-ashkenaz-weekday-maariv-ledavid</t>
+        </is>
+      </c>
+      <c r="D189" s="12" t="n">
+        <v>282</v>
+      </c>
+      <c r="E189" s="12" t="inlineStr">
+        <is>
+          <t>Weekday / Maariv / LeDavid</t>
+        </is>
+      </c>
+      <c r="F189" s="18" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="190" ht="25" customHeight="1">
+      <c r="A190" s="8" t="inlineStr">
+        <is>
+          <t>Maariv</t>
+        </is>
+      </c>
+      <c r="B190" s="8" t="inlineStr">
+        <is>
+          <t>Mourner's Kaddish</t>
+        </is>
+      </c>
+      <c r="C190" s="8" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-ashkenaz-weekday-maariv-mourner-s-kaddish</t>
+        </is>
+      </c>
+      <c r="D190" s="8" t="n">
+        <v>281</v>
+      </c>
+      <c r="E190" s="8" t="inlineStr">
+        <is>
+          <t>Weekday / Maariv / Mourner's Kaddish</t>
+        </is>
+      </c>
+      <c r="F190" s="19" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="191" ht="25" customHeight="1">
+      <c r="A191" s="12" t="inlineStr">
+        <is>
+          <t>Maariv</t>
+        </is>
+      </c>
+      <c r="B191" s="12" t="inlineStr">
+        <is>
+          <t>Vehu Rachum</t>
+        </is>
+      </c>
+      <c r="C191" s="12" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-ashkenaz-weekday-maariv-vehu-rachum</t>
+        </is>
+      </c>
+      <c r="D191" s="12" t="n">
+        <v>258</v>
+      </c>
+      <c r="E191" s="12" t="inlineStr">
+        <is>
+          <t>Weekday / Maariv / Vehu Rachum</t>
+        </is>
+      </c>
+      <c r="F191" s="18" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
+    </row>
+    <row r="192" ht="25" customHeight="1">
+      <c r="A192" s="8" t="inlineStr">
+        <is>
+          <t>Maariv</t>
+        </is>
+      </c>
+      <c r="B192" s="8" t="inlineStr">
+        <is>
+          <t>Motzaei Shabbat</t>
+        </is>
+      </c>
+      <c r="C192" s="8" t="inlineStr">
+        <is>
+          <t>sefaria-siddur-sefard-weekday-maariv-motzaei-shabbat</t>
+        </is>
+      </c>
+      <c r="D192" s="8" t="n">
+        <v>350</v>
+      </c>
+      <c r="E192" s="8" t="inlineStr">
+        <is>
+          <t>Weekday Maariv / Motzaei Shabbat</t>
+        </is>
+      </c>
+      <c r="F192" s="19" t="inlineStr">
+        <is>
+          <t>Open review row</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:F7"/>
+  <autoFilter ref="A4:F192"/>
   <mergeCells count="2">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F5" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F6" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F7" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F8" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F9" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F10" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F11" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F12" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F13" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F14" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F15" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F16" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F17" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F18" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F19" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F20" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F21" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F22" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F23" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F24" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F25" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F26" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F27" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F28" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F29" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F30" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F31" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F32" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F33" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F34" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F35" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F36" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F37" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F38" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F39" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F40" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F41" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F42" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F43" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F44" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F45" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F46" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F47" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F48" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F49" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F50" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F51" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F52" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F53" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F54" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F55" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F56" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F57" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F58" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F59" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F60" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F61" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F62" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F63" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F64" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F65" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F66" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F67" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F68" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F69" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F70" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F71" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F72" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F73" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F74" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F75" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F76" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F77" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F78" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F79" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F80" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F81" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F82" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F83" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F84" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F85" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F86" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F87" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F88" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F89" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F90" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F91" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F92" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F93" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F94" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F95" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F96" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F97" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F98" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F99" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F100" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F101" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F102" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F103" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F104" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F105" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F106" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F107" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F108" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F109" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F110" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F111" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F112" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F113" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F114" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F115" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F116" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F117" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F118" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F119" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F120" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F121" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F122" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F123" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F124" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F125" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F126" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F127" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F128" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F129" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F130" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F131" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F132" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F133" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F134" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F135" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F136" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F137" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F138" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F139" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F140" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F141" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F142" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F143" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F144" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F145" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F146" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F147" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F148" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F149" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F150" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F151" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F152" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F153" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F154" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F155" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F156" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F157" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F158" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F159" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F160" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F161" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F162" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F163" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F164" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F165" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F166" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F167" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F168" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F169" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F170" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F171" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F172" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F173" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F174" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F175" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F176" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F177" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F178" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F179" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F180" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F181" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F182" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F183" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F184" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F185" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F186" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F187" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F188" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F189" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F190" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F191" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F192" r:id="rId188"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>